--- a/Sajjad data/by_country_and_state/USA/FL.xlsx
+++ b/Sajjad data/by_country_and_state/USA/FL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="953">
   <si>
     <t>Business Name</t>
   </si>
@@ -1220,6 +1220,1656 @@
   </si>
   <si>
     <t>2026-10-24T19:45:40.144Z</t>
+  </si>
+  <si>
+    <t>GutiDental</t>
+  </si>
+  <si>
+    <t>(305) 362-5559</t>
+  </si>
+  <si>
+    <t>3822 W 16th Ave, Hialeah, FL 33012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/GutiDental/data=!4m7!3m6!1s0x88d9ba568c44e58d:0xc918c46f59ec7b1b!8m2!3d25.8563049!4d-80.3148881!16s%2Fg%2F1tdgw5zw!19sChIJjeVEjFa62YgRG3vsWW_EGMk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:17:54.690Z</t>
+  </si>
+  <si>
+    <t>My Dentist, Inc.</t>
+  </si>
+  <si>
+    <t>(305) 557-5888</t>
+  </si>
+  <si>
+    <t>7000 W 12th Ave Ste 6, Hialeah, FL 33014</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/My+Dentist,+Inc./data=!4m7!3m6!1s0x88d9bb5afe76e9d3:0xdc11cf8ebe3b7b45!8m2!3d25.8862864!4d-80.3089192!16s%2Fg%2F11hsy0st5g!19sChIJ0-l2_lq72YgRRXs7vo7PEdw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:18:32.434Z</t>
+  </si>
+  <si>
+    <t>New Family Dentistry</t>
+  </si>
+  <si>
+    <t>(305) 557-6968</t>
+  </si>
+  <si>
+    <t>1410 W 68th St, Hialeah, FL 33014</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/New+Family+Dentistry/data=!4m7!3m6!1s0x88d9badd13b62dcb:0x9b8a4f7a86d331d2!8m2!3d25.8839332!4d-80.312039!16s%2Fg%2F1tk68h1f!19sChIJyy22E9262YgR0jHThnpPips?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:11.206Z</t>
+  </si>
+  <si>
+    <t>Dr Sergio A Vega DMD</t>
+  </si>
+  <si>
+    <t>(305) 903-7519</t>
+  </si>
+  <si>
+    <t>15802 NW 57th Ave, Miami Lakes, FL 33014</t>
+  </si>
+  <si>
+    <t>Miami Lakes</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Sergio+A+Vega+DMD/data=!4m7!3m6!1s0x88d9a545da4b1751:0x65c474dfbe8dde3c!8m2!3d25.9176093!4d-80.2935744!16s%2Fg%2F11b6jjm2zp!19sChIJURdL2kWl2YgRPN6Nvt90xGU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:10.396Z</t>
+  </si>
+  <si>
+    <t>Westland Mall Dental, P.A.</t>
+  </si>
+  <si>
+    <t>(305) 828-7779</t>
+  </si>
+  <si>
+    <t>1665 W 49th St #1484, Hialeah, FL 33012</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Westland+Mall+Dental,+P.A./data=!4m7!3m6!1s0x88d9bafce8d79109:0x9aee3bd36e5fca98!8m2!3d25.8679657!4d-80.3186606!16s%2Fg%2F1trrd_rg!19sChIJCZHX6Py62YgRmMpfbtM77po?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:13.400Z</t>
+  </si>
+  <si>
+    <t>Dr. Zulima Munoz, DDS</t>
+  </si>
+  <si>
+    <t>(305) 556-9020</t>
+  </si>
+  <si>
+    <t>7150 W 20th Ave, Hialeah, FL 33016</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Zulima+Munoz,+DDS/data=!4m7!3m6!1s0x88d9bb2112f34fff:0x869175eb2b0bcd4a!8m2!3d25.8868312!4d-80.3254016!16s%2Fg%2F1hc908pg_!19sChIJ_0_zEiG72YgRSs0LK-t1kYY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:17.022Z</t>
+  </si>
+  <si>
+    <t>Taylor Orthodontics</t>
+  </si>
+  <si>
+    <t>(305) 822-7086</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>16375 NW 67th Ave, Hialeah, FL 33014</t>
+  </si>
+  <si>
+    <t>Saturday8:30 AM–6:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Taylor+Orthodontics/data=!4m7!3m6!1s0x88d9a53b46c0af85:0xd81bb8cd1d3be341!8m2!3d25.9220202!4d-80.3088392!16s%2Fg%2F1xn_p5b5!19sChIJha_ARjul2YgRQeM7Hc24G9g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:32.618Z</t>
+  </si>
+  <si>
+    <t>Fausto Nicieza PA</t>
+  </si>
+  <si>
+    <t>(305) 888-8260</t>
+  </si>
+  <si>
+    <t>1491 E 4th Ave, Hialeah, FL 33010</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fausto+Nicieza+PA/data=!4m7!3m6!1s0x88d9b09f01533473:0x61a96c7f110c9fce!8m2!3d25.8354967!4d-80.2736628!16s%2Fg%2F1vlqq_v9!19sChIJczRTAZ-w2YgRzp8MEX9sqWE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:35.379Z</t>
+  </si>
+  <si>
+    <t>Victores Norma DDS</t>
+  </si>
+  <si>
+    <t>(305) 558-7161</t>
+  </si>
+  <si>
+    <t>285 W 49th St Ste A, Hialeah, FL 33012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Victores+Norma+DDS/data=!4m7!3m6!1s0x88d9ba8561fc470f:0x8097df0cdba72223!8m2!3d25.8669996!4d-80.2878577!16s%2Fg%2F1tj5lzc2!19sChIJD0f8YYW62YgRIyKn2wzfl4A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:40.499Z</t>
+  </si>
+  <si>
+    <t>Perfect Smile and Implant Center | Dental Clinic</t>
+  </si>
+  <si>
+    <t>(305) 474-0400</t>
+  </si>
+  <si>
+    <t>18652 NW 67th Ave, Hialeah, FL 33015</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Perfect+Smile+and+Implant+Center+%7C+Dental+Clinic/data=!4m7!3m6!1s0x88d9a50faf95e2af:0x401215ad7cd9de40!8m2!3d25.9440325!4d-80.3087368!16s%2Fg%2F11f50x4g32!19sChIJr-KVrw-l2YgRQN7ZfK0VEkA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:05.475Z</t>
+  </si>
+  <si>
+    <t>Edelio Gonzalez DMD PA</t>
+  </si>
+  <si>
+    <t>(305) 826-9642</t>
+  </si>
+  <si>
+    <t>1191 W 37th St, Hialeah, FL 33012</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Edelio+Gonzalez+DMD+PA/data=!4m7!3m6!1s0x88d9ba591c330c1f:0x321193167a628ff1!8m2!3d25.8555928!4d-80.3061224!16s%2Fg%2F1td018rd!19sChIJHwwzHFm62YgR8Y9iehaTETI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:24.162Z</t>
+  </si>
+  <si>
+    <t>PALMETTO DENTAL CARE INC.</t>
+  </si>
+  <si>
+    <t>(786) 257-1646</t>
+  </si>
+  <si>
+    <t>1955 W 68th St, Hialeah, FL 33014</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/PALMETTO+DENTAL+CARE+INC./data=!4m7!3m6!1s0x88d9bba588338273:0x3ab32be270e47c87!8m2!3d25.8849792!4d-80.3222351!16s%2Fg%2F11p64tzm91!19sChIJc4IziKW72YgRh3zkcOIrszo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:29.249Z</t>
+  </si>
+  <si>
+    <t>Dr. Manuel E. Costa, DDS</t>
+  </si>
+  <si>
+    <t>(305) 769-0252</t>
+  </si>
+  <si>
+    <t>791 E 48th St, Hialeah, FL 33013</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Manuel+E.+Costa,+DDS/data=!4m7!3m6!1s0x88d9b07a97e5dfed:0x521e213f4f8ad1a8!8m2!3d25.8666262!4d-80.267016!16s%2Fg%2F1tlnf7h9!19sChIJ7d_ll3qw2YgRqNGKTz8hHlI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:32.346Z</t>
+  </si>
+  <si>
+    <t>Superior Dental</t>
+  </si>
+  <si>
+    <t>(786) 360-6262</t>
+  </si>
+  <si>
+    <t>148 Hialeah Dr, Hialeah, FL 33010</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–1 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Superior+Dental/data=!4m7!3m6!1s0x88d9ba086ad681d5:0xf7c78e943c4381ea!8m2!3d25.8225747!4d-80.2781631!16s%2Fg%2F11bzz3xfdx!19sChIJ1YHWagi62YgR6oFDPJSOx_c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:29.960Z</t>
+  </si>
+  <si>
+    <t>Amor Dental Institute | Dr Rennan Amorim</t>
+  </si>
+  <si>
+    <t>(929) 732-8806</t>
+  </si>
+  <si>
+    <t>908 St Lucie W Blvd, Port St. Lucie, FL 34986</t>
+  </si>
+  <si>
+    <t>Port St. Lucie</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Amor+Dental+Institute+%7C+Dr+Rennan+Amorim/data=!4m7!3m6!1s0x88deed8c6f358bb1:0x7517fa8f1622f55a!8m2!3d27.3168016!4d-80.3812157!16s%2Fg%2F11wbv244f0!19sChIJsYs1b4zt3ogRWvUiFo_6F3U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:40.940Z</t>
+  </si>
+  <si>
+    <t>DENTALFIXER, LLC</t>
+  </si>
+  <si>
+    <t>(904) 895-7545</t>
+  </si>
+  <si>
+    <t>120 E Aldea St, Port St. Lucie, FL 34952</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DENTALFIXER,+LLC/data=!4m7!3m6!1s0x88deefd717af44c5:0x2291aef851c13f82!8m2!3d27.3239834!4d-80.3246095!16s%2Fg%2F11n3wryvw_!19sChIJxUSvF9fv3ogRgj_BUfiukSI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:43.781Z</t>
+  </si>
+  <si>
+    <t>Forever Smiles Children's Dentistry</t>
+  </si>
+  <si>
+    <t>(772) 462-3800</t>
+  </si>
+  <si>
+    <t>537 NW Lake Whitney Pl Ste 101, Port St. Lucie, FL 34986</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Forever+Smiles+Children%27s+Dentistry/data=!4m7!3m6!1s0x88deec7935cd9939:0xe4eada5ca2c81761!8m2!3d27.317242!4d-80.4043809!16s%2Fg%2F11g6ht6q5l!19sChIJOZnNNXns3ogRYRfIolza6uQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:23:52.779Z</t>
+  </si>
+  <si>
+    <t>Kid's Place Pediatrics Pa</t>
+  </si>
+  <si>
+    <t>(772) 237-4518</t>
+  </si>
+  <si>
+    <t>Pediatrician</t>
+  </si>
+  <si>
+    <t>466 SW Port St Lucie Blvd, Port St. Lucie, FL 34953</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kid%27s+Place+Pediatrics+Pa/data=!4m7!3m6!1s0x88dee97c651c1dc7:0x23bb8939ba1c5e83!8m2!3d27.2706955!4d-80.3604314!16s%2Fg%2F126294k02!19sChIJxx0cZXzp3ogRg14cujmJuyM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:06.288Z</t>
+  </si>
+  <si>
+    <t>Braces for Us</t>
+  </si>
+  <si>
+    <t>(772) 344-7771</t>
+  </si>
+  <si>
+    <t>1620 SW Bayshore Blvd, Port St. Lucie, FL 34984</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Braces+for+Us/data=!4m7!3m6!1s0x88deebe1fdae9401:0x5c1de5180572b8ad!8m2!3d27.2923183!4d-80.3663253!16s%2Fg%2F1ttdz7zb!19sChIJAZSu_eHr3ogRrbhyBRjlHVw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:22.771Z</t>
+  </si>
+  <si>
+    <t>Icon Dentistry</t>
+  </si>
+  <si>
+    <t>(772) 344-3300</t>
+  </si>
+  <si>
+    <t>1707 St Lucie W Blvd ste. 126, Port St. Lucie, FL 34986</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Icon+Dentistry/data=!4m7!3m6!1s0x88deed00714ff26d:0xef0a3aab944dc4a1!8m2!3d27.3139019!4d-80.4047544!16s%2Fg%2F11wxfz6wzn!19sChIJbfJPcQDt3ogRocRNlKs6Cu8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:41.725Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Link</t>
+  </si>
+  <si>
+    <t>(772) 918-9568</t>
+  </si>
+  <si>
+    <t>510 NW Peacock Blvd Unit 107, Port St. Lucie, FL 34986</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Link/data=!4m7!3m6!1s0x88deed71f99ed8a5:0x9de5bb609b9e675c!8m2!3d27.3257856!4d-80.4087951!16s%2Fg%2F11p1jncnvs!19sChIJpdie-XHt3ogRXGeem2C75Z0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:57.821Z</t>
+  </si>
+  <si>
+    <t>Yazji Manhal Dds</t>
+  </si>
+  <si>
+    <t>(772) 785-9515</t>
+  </si>
+  <si>
+    <t>910 St Lucie W Blvd, Port St. Lucie, FL 34986</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yazji+Manhal+Dds/data=!4m7!3m6!1s0x88deed087670e85d:0xcce699b248930e3a!8m2!3d27.3167592!4d-80.3812403!16s%2Fg%2F11y6kp935s!19sChIJXehwdgjt3ogROg6TSLKZ5sw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:26:02.637Z</t>
+  </si>
+  <si>
+    <t>RightSmile Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(877) 415-0162</t>
+  </si>
+  <si>
+    <t>1669 SE South Niemeyer Cir, Port St. Lucie, FL 34952</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/RightSmile+Teeth+Whitening/data=!4m7!3m6!1s0x88dee8cae71d90f9:0x8051bf36b962b1a9!8m2!3d27.3041906!4d-80.3013294!16s%2Fg%2F1vfwdp33!19sChIJ-ZAd58ro3ogRqbFiuTa_UYA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:27:46.935Z</t>
+  </si>
+  <si>
+    <t>Lager, Andrew DMD</t>
+  </si>
+  <si>
+    <t>(772) 878-7300</t>
+  </si>
+  <si>
+    <t>1420 St Lucie W Blvd, Port St. Lucie, FL 34986</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lager,+Andrew+DMD/data=!4m7!3m6!1s0x88deec7500a9ed33:0xbfc8c028abc4175c!8m2!3d27.3146583!4d-80.3909224!16s%2Fg%2F1th82rzp!19sChIJM-2pAHXs3ogRXBfEqyjAyL8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:29:08.695Z</t>
+  </si>
+  <si>
+    <t>Cape Coral Dental Center</t>
+  </si>
+  <si>
+    <t>(239) 312-9060</t>
+  </si>
+  <si>
+    <t>4424 Del Prado Blvd S, Cape Coral, FL 33904</t>
+  </si>
+  <si>
+    <t>Cape Coral</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cape+Coral+Dental+Center/data=!4m7!3m6!1s0x88db41b685ce4fe1:0x2f37f93acb55c109!8m2!3d26.5692443!4d-81.9443014!16s%2Fg%2F11pc7xdgsm!19sChIJ4U_OhbZB24gRCcFVyzr5Ny8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:29:21.882Z</t>
+  </si>
+  <si>
+    <t>Family Health Center of SWFL - Dental</t>
+  </si>
+  <si>
+    <t>(239) 314-1616</t>
+  </si>
+  <si>
+    <t>Medical Center</t>
+  </si>
+  <si>
+    <t>316 Del Prado Blvd S, Cape Coral, FL 33990</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Health+Center+of+SWFL+-+Dental/data=!4m7!3m6!1s0x88db413a837f9a43:0xa6cfc4aa48a176a6!8m2!3d26.6455035!4d-81.941351!16s%2Fg%2F11n0rc3fxc!19sChIJQ5p_gzpB24gRpnahSKrEz6Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:29:24.332Z</t>
+  </si>
+  <si>
+    <t>Gregg McNeal, DDS</t>
+  </si>
+  <si>
+    <t>(239) 542-1800</t>
+  </si>
+  <si>
+    <t>643 Cape Coral Pkwy E #101A, Cape Coral, FL 33904</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gregg+McNeal,+DDS/data=!4m7!3m6!1s0x88db38aeba7e0a2b:0xbbe18d19a62bfbab!8m2!3d26.5631209!4d-81.960046!16s%2Fg%2F1thz2gjp!19sChIJKwp-uq4424gRq_srphmN4bs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:20.224Z</t>
+  </si>
+  <si>
+    <t>Dr. Dennis W. Dalton, DDS</t>
+  </si>
+  <si>
+    <t>(239) 549-5778</t>
+  </si>
+  <si>
+    <t>4401 SE 15th Ave, Cape Coral, FL 33904</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Dennis+W.+Dalton,+DDS/data=!4m7!3m6!1s0x88db40a849b945f7:0x2f91c084b10d6bf0!8m2!3d26.5703662!4d-81.9449061!16s%2Fg%2F1tknl7p5!19sChIJ90W5SahA24gR8GsNsYTAkS8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:41.631Z</t>
+  </si>
+  <si>
+    <t>Family and Cosmetic Dentistry</t>
+  </si>
+  <si>
+    <t>(239) 542-3925</t>
+  </si>
+  <si>
+    <t>1338 Lafayette St, Cape Coral, FL 33904</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+and+Cosmetic+Dentistry/data=!4m7!3m6!1s0x88db3fd6bdd262b5:0x6d577e27a3d01b81!8m2!3d26.5614257!4d-81.9471924!16s%2Fg%2F11q8v41ysl!19sChIJtWLSvdY_24gRgRvQoyd-V20?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:44.293Z</t>
+  </si>
+  <si>
+    <t>Ms Childrens Dentistry</t>
+  </si>
+  <si>
+    <t>(305) 275-7599</t>
+  </si>
+  <si>
+    <t>1715 Cape Coral Pkwy W, Cape Coral, FL 33914</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ms+Childrens+Dentistry/data=!4m7!3m6!1s0x88db38705c673d23:0xdd9ea6edaa1850e5!8m2!3d26.5633175!4d-82.0096633!16s%2Fg%2F1tjtk21q!19sChIJIz1nXHA424gR5VAYqu2mnt0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:21.830Z</t>
+  </si>
+  <si>
+    <t>Michaud Christie L DDS</t>
+  </si>
+  <si>
+    <t>(239) 540-3881</t>
+  </si>
+  <si>
+    <t>1715 Cape Coral Pkwy W #11, Cape Coral, FL 33914</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michaud+Christie+L+DDS/data=!4m7!3m6!1s0x88db38705c673d23:0xf5493fd135806591!8m2!3d26.5633175!4d-82.0096633!16s%2Fg%2F1hc5k699m!19sChIJIz1nXHA424gRkWWANdE_SfU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:24.905Z</t>
+  </si>
+  <si>
+    <t>Dr. Tyler Phillips</t>
+  </si>
+  <si>
+    <t>(239) 652-2039</t>
+  </si>
+  <si>
+    <t>2609 Santa Barbara Blvd Lee, Cape Coral, FL 33914</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tyler+Phillips/data=!4m7!3m6!1s0x88db473d0d6ff8e5:0xe38de9c125fd5b!8m2!3d26.60338!4d-81.97381!16s%2Fg%2F11rwxg3h4d!19sChIJ5fhvDT1H24gRW_0lwemN4wA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:47.528Z</t>
+  </si>
+  <si>
+    <t>Dental Emergency Source</t>
+  </si>
+  <si>
+    <t>(239) 448-0551</t>
+  </si>
+  <si>
+    <t>936-940 Country Club Blvd, Cape Coral, FL 33990</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Emergency+Source/data=!4m7!3m6!1s0x88db41d617589011:0xeada70f864eb1c19!8m2!3d26.6346545!4d-81.9521428!16s%2Fg%2F11p1b1h6rp!19sChIJEZBYF9ZB24gRGRzrZPhw2uo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:16.867Z</t>
+  </si>
+  <si>
+    <t>Dr. Jhony Espinoza</t>
+  </si>
+  <si>
+    <t>(239) 837-7002</t>
+  </si>
+  <si>
+    <t>1751 NE Pine Island Rd #130, Cape Coral, FL 33909</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jhony+Espinoza/data=!4m7!3m6!1s0x88db41d37b1a9ba3:0xee221c117426fda5!8m2!3d26.6714701!4d-81.9370759!16s%2Fg%2F11b7y84ys6!19sChIJo5sae9NB24gRpf0mdBEcIu4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:40.747Z</t>
+  </si>
+  <si>
+    <t>Smile Envy</t>
+  </si>
+  <si>
+    <t>(239) 291-8093</t>
+  </si>
+  <si>
+    <t>519 SW Pine Island Rd Inside SalonPlex, Cape Coral, FL 33991</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smile+Envy/data=!4m7!3m6!1s0x88db47af9ba6d189:0xd109cd4f36e355e1!8m2!3d26.65003!4d-81.9865042!16s%2Fg%2F11vyr63sjb!19sChIJidGmm69H24gR4VXjNk_NCdE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:34:24.147Z</t>
+  </si>
+  <si>
+    <t>Dental Center of Tallahassee.</t>
+  </si>
+  <si>
+    <t>(850) 877-3164</t>
+  </si>
+  <si>
+    <t>3614 Mahan Dr, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>Tallahassee</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Center+of+Tallahassee./data=!4m7!3m6!1s0x88ec5ee90d32c2c9:0xe60df0c528e13ab9!8m2!3d30.4651514!4d-84.2131846!16s%2Fg%2F1263nmvqh!19sChIJycIyDele7IgRuTrhKMXwDeY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:34:41.603Z</t>
+  </si>
+  <si>
+    <t>Faith Dental Center</t>
+  </si>
+  <si>
+    <t>(833) 205-2558</t>
+  </si>
+  <si>
+    <t>1100 E Tennessee St, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Faith+Dental+Center/data=!4m7!3m6!1s0x88ec5f818d492e63:0xc82b3b874c4ab8b9!8m2!3d30.4472648!4d-84.2645533!16s%2Fg%2F1hc1dytwb!19sChIJYy5JjYFf7IgRubhKTIc7K8g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:34:44.177Z</t>
+  </si>
+  <si>
+    <t>Chichetti Richard DMD</t>
+  </si>
+  <si>
+    <t>(850) 386-2400</t>
+  </si>
+  <si>
+    <t>1305 Thomaswood Dr, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Chichetti+Richard+DMD/data=!4m7!3m6!1s0x88ec58b463fa7b65:0xf3218e1806781eb8!8m2!3d30.4964712!4d-84.2532871!16s%2Fg%2F1tdzmcwd!19sChIJZXv6Y7RY7IgRuB54BhiOIfM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:02.935Z</t>
+  </si>
+  <si>
+    <t>Benjamin James Grooters</t>
+  </si>
+  <si>
+    <t>(850) 385-5297</t>
+  </si>
+  <si>
+    <t>237 John Knox Rd, Tallahassee, FL 32303</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Benjamin+James+Grooters/data=!4m7!3m6!1s0x88ecf5ed7bfc6f2d:0x6a286331b092c903!8m2!3d30.4743424!4d-84.2808864!16s%2Fg%2F11kjq6hlfb!19sChIJLW_8e-317IgRA8mSsDFjKGo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:05.294Z</t>
+  </si>
+  <si>
+    <t>Dr. John A. Bidwell, DDS.</t>
+  </si>
+  <si>
+    <t>(850) 404-6450</t>
+  </si>
+  <si>
+    <t>912 Railroad Ave, Tallahassee, FL 32310</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+John+A.+Bidwell,+DDS./data=!4m7!3m6!1s0x88ecf56ce9e99867:0x2e057ebe1832f694!8m2!3d30.4338902!4d-84.2901471!16s%2Fg%2F1tf6hgnp!19sChIJZ5jp6Wz17IgRlPYyGL5-BS4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:07.593Z</t>
+  </si>
+  <si>
+    <t>Pediatric Dentist Tallahassee.</t>
+  </si>
+  <si>
+    <t>(850) 878-1177</t>
+  </si>
+  <si>
+    <t>2424 E Plaza Dr, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pediatric+Dentist+Tallahassee./data=!4m7!3m6!1s0x88ec5f0550a0a6c5:0x557d810079cf6d4c!8m2!3d30.4578422!4d-84.238684!16s%2Fg%2F11ddyj1dp0!19sChIJxaagUAVf7IgRTG3PeQCBfVU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:34.492Z</t>
+  </si>
+  <si>
+    <t>Dr. Kenneth B. Carey, DMD</t>
+  </si>
+  <si>
+    <t>(850) 893-5177</t>
+  </si>
+  <si>
+    <t>1272 Timberlane Rd B, Tallahassee, FL 32312</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kenneth+B.+Carey,+DMD/data=!4m7!3m6!1s0x88ec58b0180fd227:0x86b6f923c8e58d72!8m2!3d30.5040125!4d-84.2588303!16s%2Fg%2F1tmgd7t2!19sChIJJ9IPGLBY7IgRco3lyCP5toY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:37.686Z</t>
+  </si>
+  <si>
+    <t>Dr. Astrid Gonzalez</t>
+  </si>
+  <si>
+    <t>(850) 792-9100</t>
+  </si>
+  <si>
+    <t>1614 W Plaza Dr, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Astrid+Gonzalez/data=!4m7!3m6!1s0x88ec5f0ff3afffff:0xa4b64471070e6d4b!8m2!3d30.457372!4d-84.2388604!16s%2Fg%2F11qgb73kn9!19sChIJ__-v8w9f7IgRS20OB3FEtqQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:40.576Z</t>
+  </si>
+  <si>
+    <t>Mc Larty E Lynn DDS</t>
+  </si>
+  <si>
+    <t>(850) 878-7200</t>
+  </si>
+  <si>
+    <t>1919 Miccosukee Rd, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mc+Larty+E+Lynn+DDS/data=!4m7!3m6!1s0x88ec5f6d5688706d:0x182e4560494161e1!8m2!3d30.459318!4d-84.2493341!16s%2Fg%2F1td33wp7!19sChIJbXCIVm1f7IgR4WFBSWBFLhg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:43.329Z</t>
+  </si>
+  <si>
+    <t>Dr. Ana Sofia Fernandez</t>
+  </si>
+  <si>
+    <t>(850) 765-3748</t>
+  </si>
+  <si>
+    <t>1771 Capital Cir NE, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ana+Sofia+Fernandez/data=!4m7!3m6!1s0x88ec5f1fb49d6e67:0x9e4f0f9c1d812a7f!8m2!3d30.4668604!4d-84.2295226!16s%2Fg%2F11rwxf3q0z!19sChIJZ26dtB9f7IgRfyqBHZwPT54?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:48.420Z</t>
+  </si>
+  <si>
+    <t>Buckingham Stephen DDS</t>
+  </si>
+  <si>
+    <t>(850) 766-4674</t>
+  </si>
+  <si>
+    <t>2768 Kinsail Dr, Tallahassee, FL 32309</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Buckingham+Stephen+DDS/data=!4m7!3m6!1s0x88ec5908838550cf:0x9c718f92c3ce3ea7!8m2!3d30.5345472!4d-84.2170135!16s%2Fg%2F1td59fqc!19sChIJz1CFgwhZ7IgRpz7Ow5KPcZw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:54.326Z</t>
+  </si>
+  <si>
+    <t>Clear Choice USA-Tallahassee</t>
+  </si>
+  <si>
+    <t>(850) 894-6369</t>
+  </si>
+  <si>
+    <t>Roofing contractor</t>
+  </si>
+  <si>
+    <t>103 Boardwalk Ln, Tallahassee, FL 32301</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clear+Choice+USA-Tallahassee/data=!4m7!3m6!1s0x88ec5e54b0435a87:0x4b13df516f9d1572!8m2!3d30.4417047!4d-84.2305906!16s%2Fg%2F1v831yfd!19sChIJh1pDsFRe7IgRchWdb1HfE0s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:19.222Z</t>
+  </si>
+  <si>
+    <t>Dr. Frank A Cerra</t>
+  </si>
+  <si>
+    <t>(850) 878-7999</t>
+  </si>
+  <si>
+    <t>Playground</t>
+  </si>
+  <si>
+    <t>1329 E Tennessee St, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Frank+A+Cerra/data=!4m7!3m6!1s0x88ec5f829b812fbd:0x23a884c8348dc57!8m2!3d30.4476378!4d-84.2611962!16s%2Fg%2F1tgwbr2p!19sChIJvS-Bm4Jf7IgRV9xIg0yIOgI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:38.564Z</t>
+  </si>
+  <si>
+    <t>Dr. Jeffrey D. Woodworth, DMD</t>
+  </si>
+  <si>
+    <t>(850) 309-0970</t>
+  </si>
+  <si>
+    <t>2274 Wednesday St, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jeffrey+D.+Woodworth,+DMD/data=!4m7!3m6!1s0x88ec5f3ab584375d:0x387efcc0d19f0936!8m2!3d30.4805277!4d-84.2386936!16s%2Fg%2F1tzvxd6r!19sChIJXTeEtTpf7IgRNgmf0cD8fjg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:40.887Z</t>
+  </si>
+  <si>
+    <t>Cooper Marion S DDS</t>
+  </si>
+  <si>
+    <t>(850) 385-0231</t>
+  </si>
+  <si>
+    <t>2027 Thomasville Rd #101, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cooper+Marion+S+DDS/data=!4m7!3m6!1s0x88ec5f610489f1bf:0xa46b21b744869c7!8m2!3d30.467817!4d-84.2671118!16s%2Fg%2F1tgcbbj2!19sChIJv_GJBGFf7IgRx2lIdBuyRgo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:45.624Z</t>
+  </si>
+  <si>
+    <t>Dennis Close, D.D.S</t>
+  </si>
+  <si>
+    <t>(850) 893-8988</t>
+  </si>
+  <si>
+    <t>2929 Kerry Forest Pkwy, Tallahassee, FL 32309</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dennis+Close,+D.D.S/data=!4m7!3m6!1s0x88ec59aa43cf87cf:0xcc70fb821e6d72d1!8m2!3d30.5398535!4d-84.2243601!16s%2Fg%2F1tdfzkbp!19sChIJz4fPQ6pZ7IgR0XJtHoL7cMw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:49.305Z</t>
+  </si>
+  <si>
+    <t>David W. Cardman, DMD</t>
+  </si>
+  <si>
+    <t>(850) 224-4151</t>
+  </si>
+  <si>
+    <t>1001 Thomasville Rd, Tallahassee, FL 32303</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/David+W.+Cardman,+DMD/data=!4m7!3m6!1s0x88ecf5a1ac6548a9:0x2af1fba66f62faa!8m2!3d30.452993!4d-84.2784257!16s%2Fg%2F11vqn9kc1y!19sChIJqUhlrKH17IgRqi_2ZrofrwI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:39:18.789Z</t>
+  </si>
+  <si>
+    <t>All Denture Studio</t>
+  </si>
+  <si>
+    <t>(407) 285-0953</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>2570 Barrington Cir #1, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/All+Denture+Studio/data=!4m7!3m6!1s0x88ec590012937bd1:0xe149aff03cb766df!8m2!3d30.5005423!4d-84.2417125!16s%2Fg%2F11yztmzb00!19sChIJ0XuTEgBZ7IgR32a3PPCvSeE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:39:55.798Z</t>
+  </si>
+  <si>
+    <t>Matthew Rasmussen</t>
+  </si>
+  <si>
+    <t>(850) 692-9200</t>
+  </si>
+  <si>
+    <t>Health care facility</t>
+  </si>
+  <si>
+    <t>4012 Kelcey Ct, Tallahassee, FL 32308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Matthew+Rasmussen/data=!4m7!3m6!1s0x88ec5ec0356eaaab:0xfde849206bdb6f2!8m2!3d30.470078!4d-84.2093317!16s%2Fg%2F11tn6lq3nj!19sChIJq6puNcBe7IgR8ra9BpKE3g8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:40:08.387Z</t>
+  </si>
+  <si>
+    <t>Bella Smile Fort Lauderdale Dentist</t>
+  </si>
+  <si>
+    <t>(954) 932-8028</t>
+  </si>
+  <si>
+    <t>2626 E Commercial Blvd, Fort Lauderdale, FL 33308</t>
+  </si>
+  <si>
+    <t>Fort Lauderdale</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bella+Smile+Fort+Lauderdale+Dentist/data=!4m7!3m6!1s0x88d9ac60ff98918b:0x301a6c1dfd349b84!8m2!3d26.1893398!4d-80.1099314!16s%2Fg%2F12q4tx22j!19sChIJi5GY_2Cs2YgRhJs0_R1sGjA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:41:45.879Z</t>
+  </si>
+  <si>
+    <t>7 Star Family Dentistry LLC</t>
+  </si>
+  <si>
+    <t>(866) 332-0379</t>
+  </si>
+  <si>
+    <t>1201 E Las Olas Blvd, Fort Lauderdale, FL 33301</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/7+Star+Family+Dentistry+LLC/data=!4m7!3m6!1s0x88d901276774b11d:0x5addbee858754ce8!8m2!3d26.1195308!4d-80.1310384!16s%2Fg%2F11zddsqfs8!19sChIJHbF0ZycB2YgR6Ex1WOi-3Vo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:43:11.418Z</t>
+  </si>
+  <si>
+    <t>LAUDERDALE DENTISTRY FOR KIDS LLC</t>
+  </si>
+  <si>
+    <t>(954) 261-7551</t>
+  </si>
+  <si>
+    <t>4500 N State Rd 7 Ste 101, Lauderdale Lakes, FL 33319</t>
+  </si>
+  <si>
+    <t>Lauderdale Lakes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/LAUDERDALE+DENTISTRY+FOR+KIDS+LLC/data=!4m7!3m6!1s0x88d905ac4cc767db:0xf67881ad698efe89!8m2!3d26.1816539!4d-80.2021876!16s%2Fg%2F11h5rngm_5!19sChIJ22fHTKwF2YgRif6Oaa2BePY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:44:45.619Z</t>
+  </si>
+  <si>
+    <t>Dr. Richard Garcia Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(954) 206-7004</t>
+  </si>
+  <si>
+    <t>2744 Davie Blvd, Fort Lauderdale, FL 33312</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Richard+Garcia+Emergency+Dental+Service/data=!4m7!3m6!1s0x88d9010318e07513:0x9c5ebc34864d7f89!8m2!3d26.1051625!4d-80.1786381!16s%2Fg%2F11ntcn3w7k!19sChIJE3XgGAMB2YgRiX9NhjS8Xpw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:46:15.755Z</t>
+  </si>
+  <si>
+    <t>Fienodontics Specialty Dental Care</t>
+  </si>
+  <si>
+    <t>(954) 491-5748</t>
+  </si>
+  <si>
+    <t>4640 N Federal Hwy Ste h, Fort Lauderdale, FL 33308</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fienodontics+Specialty+Dental+Care/data=!4m7!3m6!1s0x88d903850d3761a7:0xfd432396fb151a99!8m2!3d26.1852572!4d-80.1170792!16s%2Fg%2F11s1w9hsg9!19sChIJp2E3DYUD2YgRmRoV-5YjQ_0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:47:40.961Z</t>
+  </si>
+  <si>
+    <t>Joseph Emanuel Pechter</t>
+  </si>
+  <si>
+    <t>(954) 367-3356</t>
+  </si>
+  <si>
+    <t>2699 Stirling Rd Ste C201, Fort Lauderdale, FL 33312</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Joseph+Emanuel+Pechter/data=!4m7!3m6!1s0x88d9aa3a98990c45:0x8f914e3594706f31!8m2!3d26.0486816!4d-80.1751267!16s%2Fg%2F11ss_41fv6!19sChIJRQyZmDqq2YgRMW9wlDVOkY8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:47:43.280Z</t>
+  </si>
+  <si>
+    <t>Pembroke Lakes Mall Dental</t>
+  </si>
+  <si>
+    <t>(954) 573-1400</t>
+  </si>
+  <si>
+    <t>11401 Pines Blvd Suite 220, Pembroke Pines, FL 33026</t>
+  </si>
+  <si>
+    <t>Pembroke Pines</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pembroke+Lakes+Mall+Dental/data=!4m7!3m6!1s0x88d9a7684f6c6051:0x51ae15f5a831de58!8m2!3d26.0103238!4d-80.3061093!16s%2Fg%2F11y1w8hz1q!19sChIJUWBsT2in2YgRWN4xqPUVrlE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:49:19.342Z</t>
+  </si>
+  <si>
+    <t>Pines Dental: Mezcua Maria A DDS</t>
+  </si>
+  <si>
+    <t>(954) 432-4101</t>
+  </si>
+  <si>
+    <t>18503 Pines Blvd #202, Hollywood, FL 33029</t>
+  </si>
+  <si>
+    <t>Hollywood</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pines+Dental:+Mezcua+Maria+A+DDS/data=!4m7!3m6!1s0x88d9a163b49b5455:0xbcb49187bc1d451d!8m2!3d26.0109233!4d-80.3958663!16s%2Fg%2F1v831xdc!19sChIJVVSbtGOh2YgRHUUdvIeRtLw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:50:23.384Z</t>
+  </si>
+  <si>
+    <t>Pembroke Pines Family Dental Center, P.A : Dr. Delroy Webb, D.M.D.</t>
+  </si>
+  <si>
+    <t>(954) 436-3900</t>
+  </si>
+  <si>
+    <t>700 N Hiatus Rd Ste 201, Pembroke Pines, FL 33026</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pembroke+Pines+Family+Dental+Center,+P.A+:+Dr.+Delroy+Webb,+D.M.D./data=!4m7!3m6!1s0x88d9a612becb4917:0x85577535da3b337d!8m2!3d26.011214!4d-80.298675!16s%2Fg%2F1vvyyws9!19sChIJF0nLvhKm2YgRfTM72jV1V4U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:51:02.517Z</t>
+  </si>
+  <si>
+    <t>Pines Dental Care</t>
+  </si>
+  <si>
+    <t>(954) 538-0047</t>
+  </si>
+  <si>
+    <t>17868 NW 2nd St, Pembroke Pines, FL 33029</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pines+Dental+Care/data=!4m7!3m6!1s0x88d9a183f36901ab:0x8eb3951f9b6ec325!8m2!3d26.0082694!4d-80.3860384!16s%2Fg%2F11vkpp60k3!19sChIJqwFp84Oh2YgRJcNumx-Vs44?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:52:40.919Z</t>
+  </si>
+  <si>
+    <t>Sun East Dental Pa</t>
+  </si>
+  <si>
+    <t>(954) 885-5351</t>
+  </si>
+  <si>
+    <t>20841 Johnson St Ste 104, Pembroke Pines, FL 33029</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sun+East+Dental+Pa/data=!4m7!3m6!1s0x88d9a17ff9c916b3:0x7c09564c637d6cb7!8m2!3d26.0156594!4d-80.4269348!16s%2Fg%2F1tf7sycv!19sChIJsxbJ-X-h2YgRt2x9Y0xWCXw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:53:07.223Z</t>
+  </si>
+  <si>
+    <t>Denise Anne Brady</t>
+  </si>
+  <si>
+    <t>(754) 217-4633</t>
+  </si>
+  <si>
+    <t>700 N Hiatus Rd #101, Pembroke Pines, FL 330265206</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denise+Anne+Brady/data=!4m7!3m6!1s0x88d9a612b6fcb6b5:0x4fcc34805a6ad0f1!8m2!3d26.0112888!4d-80.2985199!16s%2Fg%2F11ty7v6l37!19sChIJtbb8thKm2YgR8dBqWoA0zE8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:54:10.620Z</t>
+  </si>
+  <si>
+    <t>Perfect Smile Dental Spa</t>
+  </si>
+  <si>
+    <t>(954) 364-7626</t>
+  </si>
+  <si>
+    <t>117 S 21st Ave, Hollywood, FL 33020</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Perfect+Smile+Dental+Spa/data=!4m7!3m6!1s0x88d9aba043827db3:0xf475b970104b51d6!8m2!3d26.0107752!4d-80.1487002!16s%2Fg%2F11c5zv5j_2!19sChIJs32CQ6Cr2YgR1lFLEHC5dfQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:55:30.985Z</t>
+  </si>
+  <si>
+    <t>Leon Pablo E DDS</t>
+  </si>
+  <si>
+    <t>(954) 981-4107</t>
+  </si>
+  <si>
+    <t>5351 Sheridan St, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Leon+Pablo+E+DDS/data=!4m7!3m6!1s0x88d9a979f8f79335:0xc468f48b867063d2!8m2!3d26.0345841!4d-80.1980889!16s%2Fg%2F1vcl4kgg!19sChIJNZP3-Hmp2YgR0mNwhov0aMQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:55:57.581Z</t>
+  </si>
+  <si>
+    <t>Feuer, Mitchell DMD</t>
+  </si>
+  <si>
+    <t>(954) 922-6281</t>
+  </si>
+  <si>
+    <t>900 S Federal Hwy, Hollywood, FL 33020</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Feuer,+Mitchell+DMD/data=!4m7!3m6!1s0x88d9ab9df52b863b:0xcb94437b7802d73b!8m2!3d26.0038461!4d-80.1430356!16s%2Fg%2F1tdfjg_m!19sChIJO4Yr9Z2r2YgRO9cCeHtDlMs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:17.538Z</t>
+  </si>
+  <si>
+    <t>Sheridan Dental Care (Dr Dorene Montero and Dr Fernando Quevedo)</t>
+  </si>
+  <si>
+    <t>(954) 964-4229</t>
+  </si>
+  <si>
+    <t>4330 Sheridan St Ste 201A, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sheridan+Dental+Care+%28Dr+Dorene+Montero+and+Dr+Fernando+Quevedo%29/data=!4m7!3m6!1s0x88d9a938fa17300f:0x3f419730424f5015!8m2!3d26.0317313!4d-80.1881811!16s%2Fg%2F11fmqb6txy!19sChIJDzAX-jip2YgRFVBPQjCXQT8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:47.197Z</t>
+  </si>
+  <si>
+    <t>Andrew J Adler, DMD</t>
+  </si>
+  <si>
+    <t>(954) 457-7637</t>
+  </si>
+  <si>
+    <t>3901 S Ocean Dr Apt 1, Hollywood, FL 33019</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Andrew+J+Adler,+DMD/data=!4m7!3m6!1s0x88d9ab5fc711c015:0x2ebf6b1ffff18fca!8m2!3d25.9886883!4d-80.1180559!16s%2Fg%2F1tcxkkkw!19sChIJFcARx1-r2YgRyo_x_x9rvy4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:56:51.653Z</t>
+  </si>
+  <si>
+    <t>Creative Dentistry</t>
+  </si>
+  <si>
+    <t>(954) 589-0750</t>
+  </si>
+  <si>
+    <t>5937 Sheridan St, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Creative+Dentistry/data=!4m7!3m6!1s0x88d9a97378403d4b:0xc0767451df6d20d9!8m2!3d26.0324559!4d-80.2071376!16s%2Fg%2F1hd_lpz0_!19sChIJSz1AeHOp2YgR2SBt31F0dsA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:02.211Z</t>
+  </si>
+  <si>
+    <t>Miramar Family Dentistry</t>
+  </si>
+  <si>
+    <t>(954) 987-7007</t>
+  </si>
+  <si>
+    <t>9720 Stirling Rd #211, Hollywood, FL 33024</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Miramar+Family+Dentistry/data=!4m7!3m6!1s0x88d9a87feef00857:0x7d996657386fccf0!8m2!3d26.0442298!4d-80.2753948!16s%2Fg%2F1261fckwt!19sChIJVwjw7n-o2YgR8MxvOFdmmX0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:57:29.041Z</t>
+  </si>
+  <si>
+    <t>Dental Care PA</t>
+  </si>
+  <si>
+    <t>(954) 777-8767</t>
+  </si>
+  <si>
+    <t>2647 Hollywood Blvd, Hollywood, FL 33020</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Care+PA/data=!4m7!3m6!1s0x88d9ab832096ba95:0x600e18a31d619186!8m2!3d26.0114531!4d-80.1608687!16s%2Fg%2F11w3l9fdd5!19sChIJlbqWIIOr2YgRhpFhHaMYDmA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:25.041Z</t>
+  </si>
+  <si>
+    <t>Dr. Steven J. Zombek, DMD</t>
+  </si>
+  <si>
+    <t>(954) 961-2695</t>
+  </si>
+  <si>
+    <t>4480 Sheridan St, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Steven+J.+Zombek,+DMD/data=!4m7!3m6!1s0x88d9a97dd76e4999:0xf59a37525c68217f!8m2!3d26.0317054!4d-80.1897296!16s%2Fg%2F1tnl25_l!19sChIJmUlu132p2YgRfyFoXFI3mvU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:39.861Z</t>
+  </si>
+  <si>
+    <t>Amazing Dental Orthodontics</t>
+  </si>
+  <si>
+    <t>(954) 589-1662</t>
+  </si>
+  <si>
+    <t>5740 Hollywood Blvd Ste 400, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Amazing+Dental+Orthodontics/data=!4m7!3m6!1s0x88d9a9de41cdb2d7:0x107d48f5468b4d11!8m2!3d26.0098728!4d-80.2031622!16s%2Fg%2F11f9v9k0sy!19sChIJ17LNQd6p2YgREU2LRvVIfRA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:42.639Z</t>
+  </si>
+  <si>
+    <t>Happy Dental Group</t>
+  </si>
+  <si>
+    <t>(954) 404-8743</t>
+  </si>
+  <si>
+    <t>5615 Sheridan St, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday9 AM–6 PM; Tuesday9 AM–6 PM; Wednesday9 AM–6 PM; Thursday9 AM–6 PM; Friday9 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Happy+Dental+Group/data=!4m7!3m6!1s0x88d9a92922271619:0xf8d649c8f0c2b155!8m2!3d26.0325103!4d-80.2011359!16s%2Fg%2F11hj6rq1pn!19sChIJGRYnIimp2YgRVbHC8MhJ1vg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:58:58.258Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Connect</t>
+  </si>
+  <si>
+    <t>(954) 872-1046</t>
+  </si>
+  <si>
+    <t>1915 FL-820, Hollywood, FL 33020</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Connect/data=!4m7!3m6!1s0x88d9abcd37131547:0xcbe5623ed4b2b190!8m2!3d26.0116534!4d-80.1455035!16s%2Fg%2F11zwls2z6b!19sChIJRxUTN82r2YgRkLGy1D5i5cs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:59:27.367Z</t>
+  </si>
+  <si>
+    <t>Smile With Zia</t>
+  </si>
+  <si>
+    <t>(954) 865-7825</t>
+  </si>
+  <si>
+    <t>2 Oakwood Blvd 190 Suite 33, Hollywood, FL 33020</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smile+With+Zia/data=!4m7!3m6!1s0x88d9ab33a99266fb:0x3d069e5e2c94619b!8m2!3d26.0392403!4d-80.1608687!16s%2Fg%2F11s4s24b_x!19sChIJ-2aSqTOr2YgRm2GULF6eBj0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:00:24.352Z</t>
+  </si>
+  <si>
+    <t>Hollywood Florida Dentist</t>
+  </si>
+  <si>
+    <t>(954) 573-2021</t>
+  </si>
+  <si>
+    <t>5740 Hollywood Blvd, Hollywood, FL 33021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hollywood+Florida+Dentist/data=!4m7!3m6!1s0x88d9a943f3fb12e1:0x9c8c228d0959d446!8m2!3d26.009866!4d-80.2031782!16s%2Fg%2F1wj_6v3t!19sChIJ4RL780Op2YgRRtRZCY0ijJw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:00:47.585Z</t>
+  </si>
+  <si>
+    <t>Hollywood Dentist</t>
+  </si>
+  <si>
+    <t>(954) 342-8315</t>
+  </si>
+  <si>
+    <t>650 S Federal Hwy, Hollywood, FL 33020</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hollywood+Dentist/data=!4m7!3m6!1s0x88d9ab9e1cff744b:0xc4fb08f37e5eabf9!8m2!3d26.0062463!4d-80.1431224!16s%2Fg%2F1tdmfpgl!19sChIJS3T_HJ6r2YgR-atefvMI-8Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:00:52.535Z</t>
+  </si>
+  <si>
+    <t>Prairie Dental Center</t>
+  </si>
+  <si>
+    <t>(352) 373-3431</t>
+  </si>
+  <si>
+    <t>6320 SW 13th St B, Gainesville, FL 32608</t>
+  </si>
+  <si>
+    <t>Gainesville</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prairie+Dental+Center/data=!4m7!3m6!1s0x88e8a25c2fead727:0x68d8d50f88fc06ab!8m2!3d29.5950579!4d-82.3395243!16s%2Fg%2F1tf6n0hy!19sChIJJ9fqL1yi6IgRqwb8iA_V2Gg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:02:17.285Z</t>
+  </si>
+  <si>
+    <t>Rodgers Family Dental</t>
+  </si>
+  <si>
+    <t>(352) 373-7373</t>
+  </si>
+  <si>
+    <t>4140 NW 27th Ln suite h, Gainesville, FL 32606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rodgers+Family+Dental/data=!4m7!3m6!1s0x88e8a5981b26752f:0x23368d0c354881f9!8m2!3d29.6782396!4d-82.3875705!16s%2Fg%2F11nbb4pdp1!19sChIJL3UmG5il6IgR-YFINQyNNiM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:03:30.940Z</t>
+  </si>
+  <si>
+    <t>Jonesville Family Dentistry</t>
+  </si>
+  <si>
+    <t>(352) 332-3080</t>
+  </si>
+  <si>
+    <t>175 NW 138th Terrace Ste 200, Newberry, FL 32669</t>
+  </si>
+  <si>
+    <t>Newberry</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jonesville+Family+Dentistry/data=!4m7!3m6!1s0x88e8bf26ba89205b:0x93304936f7547b76!8m2!3d29.6551112!4d-82.4898451!16s%2Fg%2F1tmcn1nc!19sChIJWyCJuia_6IgRdntU9zZJMJM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:03:39.570Z</t>
+  </si>
+  <si>
+    <t>Thaler Townsend</t>
+  </si>
+  <si>
+    <t>(352) 378-2233</t>
+  </si>
+  <si>
+    <t>3500 W University Ave, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Thaler+Townsend/data=!4m7!3m6!1s0x88e8a35b1e4fe395:0x58108cfe395d0571!8m2!3d29.6523387!4d-82.374888!16s%2Fg%2F1wh4gpfn!19sChIJleNPHluj6IgRcQVdOf6MEFg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:03:46.760Z</t>
+  </si>
+  <si>
+    <t>Gator Family Dentistry</t>
+  </si>
+  <si>
+    <t>(352) 364-9800</t>
+  </si>
+  <si>
+    <t>230 NW 76 Dr # B, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gator+Family+Dentistry/data=!4m7!3m6!1s0x88e8bc85bfd04877:0x3cc0795d487e6833!8m2!3d29.655021!4d-82.425032!16s%2Fg%2F11f_p2w4_9!19sChIJd0jQv4W86IgRM2h-SF15wDw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:04:08.216Z</t>
+  </si>
+  <si>
+    <t>Aesthetic &amp; Cosmetic Dentistry</t>
+  </si>
+  <si>
+    <t>(352) 373-3263</t>
+  </si>
+  <si>
+    <t>821 NW 13th St A, Gainesville, FL 32601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aesthetic+%26+Cosmetic+Dentistry/data=!4m7!3m6!1s0x88e8a387566fc8a9:0x2bea3d7d768eceac!8m2!3d29.659953!4d-82.338839!16s%2Fg%2F1thxlx6h!19sChIJqchvVoej6IgRrM6Odn096is?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:04:37.529Z</t>
+  </si>
+  <si>
+    <t>Millhopper Pediatric Dentistry: Beaufait N Nguyen DDS</t>
+  </si>
+  <si>
+    <t>(352) 336-3939</t>
+  </si>
+  <si>
+    <t>2341 NW 41 St A, Gainesville, FL 32606</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Millhopper+Pediatric+Dentistry:+Beaufait+N+Nguyen+DDS/data=!4m7!3m6!1s0x88e8a4ad7dc3becf:0x2657abce5ea97e13!8m2!3d29.6749499!4d-82.3859108!16s%2Fg%2F1tj1nblq!19sChIJz77Dfa2k6IgRE36pXs6rVyY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:04:53.535Z</t>
+  </si>
+  <si>
+    <t>Martin Kids Dental of Lake City.</t>
+  </si>
+  <si>
+    <t>(386) 752-8200</t>
+  </si>
+  <si>
+    <t>973 FL-47, Lake City, FL 32025</t>
+  </si>
+  <si>
+    <t>Lake City</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Martin+Kids+Dental+of+Lake+City./data=!4m7!3m6!1s0x88ef398b413391ad:0xeb2904cf77b6159b!8m2!3d30.1580725!4d-82.6456481!16s%2Fg%2F1tjh062h!19sChIJrZEzQYs574gRmxW2d88EKes?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:04:55.971Z</t>
+  </si>
+  <si>
+    <t>Dr. Whitney Schaff</t>
+  </si>
+  <si>
+    <t>(352) 331-1004</t>
+  </si>
+  <si>
+    <t>6110 NW 1st Pl Suite A, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Whitney+Schaff/data=!4m7!3m6!1s0x88e8bca2e767def9:0x4134951e7c333669!8m2!3d29.6540502!4d-82.4079821!16s%2Fg%2F11rwxg5t14!19sChIJ-d5n56K86IgRaTYzfB6VNEE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:04:58.434Z</t>
+  </si>
+  <si>
+    <t>Catalanotto Frank DDS</t>
+  </si>
+  <si>
+    <t>(352) 265-8075</t>
+  </si>
+  <si>
+    <t>1600 SW Archer Rd, Gainesville, FL 32608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Catalanotto+Frank+DDS/data=!4m7!3m6!1s0x88e8a39e42a9d089:0x8c998d141e660aaa!8m2!3d29.6400842!4d-82.3443413!16s%2Fg%2F1v470577!19sChIJidCpQp6j6IgRqgpmHhSNmYw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:00.447Z</t>
+  </si>
+  <si>
+    <t>Abimbola O Adewumi</t>
+  </si>
+  <si>
+    <t>(352) 273-7643</t>
+  </si>
+  <si>
+    <t>1395 Center Drive in D1-40 In GPS use 1600, SW Archer Rd, Gainesville, FL 32610</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Abimbola+O+Adewumi/data=!4m7!3m6!1s0x88e8a39e42a9d089:0xf4f297ad61583732!8m2!3d29.6398333!4d-82.3434662!16s%2Fg%2F1thr7_gv!19sChIJidCpQp6j6IgRMjdYYa2X8vQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:03.778Z</t>
+  </si>
+  <si>
+    <t>Dr. Elizabeth A. Hill, DDS</t>
+  </si>
+  <si>
+    <t>(352) 373-7582</t>
+  </si>
+  <si>
+    <t>1000 NW 8th Ave, Gainesville, FL 32601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Elizabeth+A.+Hill,+DDS/data=!4m7!3m6!1s0x88e8a38789b42219:0x88a6e27b6564050f!8m2!3d29.6597916!4d-82.3353863!16s%2Fg%2F1v6wq4gh!19sChIJGSK0iYej6IgRDwVkZXvipog?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:06.633Z</t>
+  </si>
+  <si>
+    <t>MICHAEL J. AGUIRRE, DDS ORTHODONTIST</t>
+  </si>
+  <si>
+    <t>(352) 681-2200</t>
+  </si>
+  <si>
+    <t>4031 NW 43rd St, Gainesville, FL 32606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MICHAEL+J.+AGUIRRE,+DDS+ORTHODONTIST/data=!4m7!3m6!1s0x88e8a5455fa91883:0xe766c9f7cf027d81!8m2!3d29.6900198!4d-82.3879301!16s%2Fg%2F11c76t7kzd!19sChIJgxipX0Wl6IgRgX0Cz_fJZuc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:22.211Z</t>
+  </si>
+  <si>
+    <t>Dr. Reid W. Montini, DMD</t>
+  </si>
+  <si>
+    <t>(352) 332-7911</t>
+  </si>
+  <si>
+    <t>7520 W University Ave # C, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Reid+W.+Montini,+DMD/data=!4m7!3m6!1s0x88e8bc9aaf1fd1af:0xf6a6095ce18cc3d!8m2!3d29.6537822!4d-82.4230802!16s%2Fg%2F1thvtjgg!19sChIJr9Efr5q86IgRPcwYzpVgag8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:24.689Z</t>
+  </si>
+  <si>
+    <t>Jacobson &amp; Martin Orthodontics</t>
+  </si>
+  <si>
+    <t>(352) 331-5132</t>
+  </si>
+  <si>
+    <t>7575 W University Ave e, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jacobson+%26+Martin+Orthodontics/data=!4m7!3m6!1s0x88e8bc8f76b562b3:0xbfa31d11b7a1ae55!8m2!3d29.6526418!4d-82.4240702!16s%2Fg%2F1vyxk771!19sChIJs2K1do-86IgRVa6htxEdo78?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:27.633Z</t>
+  </si>
+  <si>
+    <t>Waldron Joseph M DDS</t>
+  </si>
+  <si>
+    <t>(352) 331-5622</t>
+  </si>
+  <si>
+    <t>611 NW 60th St Ste A, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Waldron+Joseph+M+DDS/data=!4m7!3m6!1s0x88e8bca3e04b9d37:0xcd4ca4f7be477661!8m2!3d29.6580562!4d-82.4060596!16s%2Fg%2F1tfpw2mh!19sChIJN51L4KO86IgRYXZHvvekTM0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:30.317Z</t>
+  </si>
+  <si>
+    <t>Dr. Natalie Mullally</t>
+  </si>
+  <si>
+    <t>(352) 336-2222</t>
+  </si>
+  <si>
+    <t>2222 NW 40th Terrace Ste b, Gainesville, FL 32605</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Natalie+Mullally/data=!4m7!3m6!1s0x88e8a4ad90f40001:0xb03842727297788d!8m2!3d29.6733681!4d-82.385074!16s%2Fg%2F11qgb7krwr!19sChIJAQD0kK2k6IgRjXiXcnJCOLA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:05:32.767Z</t>
+  </si>
+  <si>
+    <t>Frank E. Lozano, D.M.D, M.S.</t>
+  </si>
+  <si>
+    <t>(352) 203-1043</t>
+  </si>
+  <si>
+    <t>4411 NW 8th Ave, Gainesville, FL 32605</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Frank+E.+Lozano,+D.M.D,+M.S./data=!4m7!3m6!1s0x88e8a4b2c17f95d7:0x34340b04cf0940b0!8m2!3d29.6592496!4d-82.3905626!16s%2Fg%2F1vmr262g!19sChIJ15V_wbKk6IgRsEAJzwQLNDQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:05.633Z</t>
+  </si>
+  <si>
+    <t>Dr. Kenneth W. Knopf, DMD</t>
+  </si>
+  <si>
+    <t>(352) 377-1705</t>
+  </si>
+  <si>
+    <t>3510 NW 43rd St, Gainesville, FL 32606</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–4 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kenneth+W.+Knopf,+DMD/data=!4m7!3m6!1s0x88e8bb4abac22faf:0x22d94507b69cd63a!8m2!3d29.6850954!4d-82.389277!16s%2Fg%2F12qh938fc!19sChIJry_Cukq76IgROtactgdF2SI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:10.354Z</t>
+  </si>
+  <si>
+    <t>Immediate Dental One</t>
+  </si>
+  <si>
+    <t>(352) 657-1859</t>
+  </si>
+  <si>
+    <t>808 FL-24, Gainesville, FL 32601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Immediate+Dental+One/data=!4m7!3m6!1s0x88e8a3b726d925af:0xeb06bb7ad70dd867!8m2!3d29.6521768!4d-82.3332169!16s%2Fg%2F11vz94p3hr!19sChIJryXZJrej6IgRZ9gN13q7Bus?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:25.392Z</t>
+  </si>
+  <si>
+    <t>Professional Designs</t>
+  </si>
+  <si>
+    <t>(352) 265-0111</t>
+  </si>
+  <si>
+    <t>1600 SW Archer Rd, Gainesville, FL 32610</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Professional+Designs/data=!4m7!3m6!1s0x88e8a39e42a9d089:0x2dbe1a7746437fd3!8m2!3d29.6400814!4d-82.343605!16s%2Fg%2F1th82sfd!19sChIJidCpQp6j6IgR039DRncavi0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:30.426Z</t>
+  </si>
+  <si>
+    <t>Dr. Jordan T. Webb, DMD</t>
+  </si>
+  <si>
+    <t>(352) 378-2555</t>
+  </si>
+  <si>
+    <t>3655 SW 2nd Ave, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jordan+T.+Webb,+DMD/data=!4m7!3m6!1s0x88e8a35aac83b6fd:0x635779348db1169b!8m2!3d29.6508669!4d-82.3776064!16s%2Fg%2F1hc4n_lms!19sChIJ_baDrFqj6IgRmxaxjTR5V2M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T23:06:39.330Z</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +3250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4323,6 +5973,4229 @@
         <v>402</v>
       </c>
     </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>403</v>
+      </c>
+      <c r="B67" t="s">
+        <v>404</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>405</v>
+      </c>
+      <c r="E67" t="s">
+        <v>389</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>131</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>44</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>406</v>
+      </c>
+      <c r="M67" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>408</v>
+      </c>
+      <c r="B68" t="s">
+        <v>409</v>
+      </c>
+      <c r="C68" t="s">
+        <v>105</v>
+      </c>
+      <c r="D68" t="s">
+        <v>410</v>
+      </c>
+      <c r="E68" t="s">
+        <v>389</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>44</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>411</v>
+      </c>
+      <c r="M68" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>413</v>
+      </c>
+      <c r="B69" t="s">
+        <v>414</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>415</v>
+      </c>
+      <c r="E69" t="s">
+        <v>389</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>301</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>44</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>416</v>
+      </c>
+      <c r="M69" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>418</v>
+      </c>
+      <c r="B70" t="s">
+        <v>419</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>420</v>
+      </c>
+      <c r="E70" t="s">
+        <v>421</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>422</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>423</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>424</v>
+      </c>
+      <c r="M70" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>426</v>
+      </c>
+      <c r="B71" t="s">
+        <v>427</v>
+      </c>
+      <c r="C71" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" t="s">
+        <v>428</v>
+      </c>
+      <c r="E71" t="s">
+        <v>389</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>429</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>430</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>431</v>
+      </c>
+      <c r="M71" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>433</v>
+      </c>
+      <c r="B72" t="s">
+        <v>434</v>
+      </c>
+      <c r="C72" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" t="s">
+        <v>435</v>
+      </c>
+      <c r="E72" t="s">
+        <v>389</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>31</v>
+      </c>
+      <c r="I72" t="s">
+        <v>188</v>
+      </c>
+      <c r="J72" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>436</v>
+      </c>
+      <c r="M72" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>438</v>
+      </c>
+      <c r="B73" t="s">
+        <v>439</v>
+      </c>
+      <c r="C73" t="s">
+        <v>440</v>
+      </c>
+      <c r="D73" t="s">
+        <v>441</v>
+      </c>
+      <c r="E73" t="s">
+        <v>389</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>442</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>443</v>
+      </c>
+      <c r="M73" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>445</v>
+      </c>
+      <c r="B74" t="s">
+        <v>446</v>
+      </c>
+      <c r="C74" t="s">
+        <v>440</v>
+      </c>
+      <c r="D74" t="s">
+        <v>447</v>
+      </c>
+      <c r="E74" t="s">
+        <v>389</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>131</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>44</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>448</v>
+      </c>
+      <c r="M74" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>450</v>
+      </c>
+      <c r="B75" t="s">
+        <v>451</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>452</v>
+      </c>
+      <c r="E75" t="s">
+        <v>389</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>162</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>453</v>
+      </c>
+      <c r="M75" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>455</v>
+      </c>
+      <c r="B76" t="s">
+        <v>456</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>457</v>
+      </c>
+      <c r="E76" t="s">
+        <v>389</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>162</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>44</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>458</v>
+      </c>
+      <c r="M76" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>460</v>
+      </c>
+      <c r="B77" t="s">
+        <v>461</v>
+      </c>
+      <c r="C77" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" t="s">
+        <v>462</v>
+      </c>
+      <c r="E77" t="s">
+        <v>389</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>89</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>430</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>463</v>
+      </c>
+      <c r="M77" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>465</v>
+      </c>
+      <c r="B78" t="s">
+        <v>466</v>
+      </c>
+      <c r="C78" t="s">
+        <v>105</v>
+      </c>
+      <c r="D78" t="s">
+        <v>467</v>
+      </c>
+      <c r="E78" t="s">
+        <v>389</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>44</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>468</v>
+      </c>
+      <c r="M78" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>470</v>
+      </c>
+      <c r="B79" t="s">
+        <v>471</v>
+      </c>
+      <c r="C79" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" t="s">
+        <v>472</v>
+      </c>
+      <c r="E79" t="s">
+        <v>389</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>301</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>44</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>473</v>
+      </c>
+      <c r="M79" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>475</v>
+      </c>
+      <c r="B80" t="s">
+        <v>476</v>
+      </c>
+      <c r="C80" t="s">
+        <v>105</v>
+      </c>
+      <c r="D80" t="s">
+        <v>477</v>
+      </c>
+      <c r="E80" t="s">
+        <v>389</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>269</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>478</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>479</v>
+      </c>
+      <c r="M80" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>481</v>
+      </c>
+      <c r="B81" t="s">
+        <v>482</v>
+      </c>
+      <c r="C81" t="s">
+        <v>105</v>
+      </c>
+      <c r="D81" t="s">
+        <v>483</v>
+      </c>
+      <c r="E81" t="s">
+        <v>484</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>44</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>485</v>
+      </c>
+      <c r="M81" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>487</v>
+      </c>
+      <c r="B82" t="s">
+        <v>488</v>
+      </c>
+      <c r="C82" t="s">
+        <v>105</v>
+      </c>
+      <c r="D82" t="s">
+        <v>489</v>
+      </c>
+      <c r="E82" t="s">
+        <v>484</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>31</v>
+      </c>
+      <c r="I82" t="s">
+        <v>188</v>
+      </c>
+      <c r="J82" t="s">
+        <v>38</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>490</v>
+      </c>
+      <c r="M82" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>492</v>
+      </c>
+      <c r="B83" t="s">
+        <v>493</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" t="s">
+        <v>494</v>
+      </c>
+      <c r="E83" t="s">
+        <v>484</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>131</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>22</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>495</v>
+      </c>
+      <c r="M83" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>497</v>
+      </c>
+      <c r="B84" t="s">
+        <v>498</v>
+      </c>
+      <c r="C84" t="s">
+        <v>499</v>
+      </c>
+      <c r="D84" t="s">
+        <v>500</v>
+      </c>
+      <c r="E84" t="s">
+        <v>484</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>131</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>44</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>501</v>
+      </c>
+      <c r="M84" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>503</v>
+      </c>
+      <c r="B85" t="s">
+        <v>504</v>
+      </c>
+      <c r="C85" t="s">
+        <v>440</v>
+      </c>
+      <c r="D85" t="s">
+        <v>505</v>
+      </c>
+      <c r="E85" t="s">
+        <v>484</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>70</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>44</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>506</v>
+      </c>
+      <c r="M85" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>508</v>
+      </c>
+      <c r="B86" t="s">
+        <v>509</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>510</v>
+      </c>
+      <c r="E86" t="s">
+        <v>484</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>301</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>44</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>511</v>
+      </c>
+      <c r="M86" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>513</v>
+      </c>
+      <c r="B87" t="s">
+        <v>514</v>
+      </c>
+      <c r="C87" t="s">
+        <v>28</v>
+      </c>
+      <c r="D87" t="s">
+        <v>515</v>
+      </c>
+      <c r="E87" t="s">
+        <v>484</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>31</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>516</v>
+      </c>
+      <c r="M87" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>518</v>
+      </c>
+      <c r="B88" t="s">
+        <v>519</v>
+      </c>
+      <c r="C88" t="s">
+        <v>28</v>
+      </c>
+      <c r="D88" t="s">
+        <v>520</v>
+      </c>
+      <c r="E88" t="s">
+        <v>484</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>31</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>521</v>
+      </c>
+      <c r="M88" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>523</v>
+      </c>
+      <c r="B89" t="s">
+        <v>524</v>
+      </c>
+      <c r="C89" t="s">
+        <v>87</v>
+      </c>
+      <c r="D89" t="s">
+        <v>525</v>
+      </c>
+      <c r="E89" t="s">
+        <v>484</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>31</v>
+      </c>
+      <c r="I89" t="s">
+        <v>188</v>
+      </c>
+      <c r="J89" t="s">
+        <v>31</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>526</v>
+      </c>
+      <c r="M89" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>528</v>
+      </c>
+      <c r="B90" t="s">
+        <v>529</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>530</v>
+      </c>
+      <c r="E90" t="s">
+        <v>484</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>119</v>
+      </c>
+      <c r="I90" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>44</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>531</v>
+      </c>
+      <c r="M90" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>533</v>
+      </c>
+      <c r="B91" t="s">
+        <v>534</v>
+      </c>
+      <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" t="s">
+        <v>535</v>
+      </c>
+      <c r="E91" t="s">
+        <v>536</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>37</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>31</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>537</v>
+      </c>
+      <c r="M91" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>539</v>
+      </c>
+      <c r="B92" t="s">
+        <v>540</v>
+      </c>
+      <c r="C92" t="s">
+        <v>541</v>
+      </c>
+      <c r="D92" t="s">
+        <v>542</v>
+      </c>
+      <c r="E92" t="s">
+        <v>536</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>543</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>44</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>544</v>
+      </c>
+      <c r="M92" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>546</v>
+      </c>
+      <c r="B93" t="s">
+        <v>547</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>548</v>
+      </c>
+      <c r="E93" t="s">
+        <v>536</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>44</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>549</v>
+      </c>
+      <c r="M93" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>551</v>
+      </c>
+      <c r="B94" t="s">
+        <v>552</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>553</v>
+      </c>
+      <c r="E94" t="s">
+        <v>536</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>162</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>44</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>554</v>
+      </c>
+      <c r="M94" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>556</v>
+      </c>
+      <c r="B95" t="s">
+        <v>557</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>558</v>
+      </c>
+      <c r="E95" t="s">
+        <v>536</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>31</v>
+      </c>
+      <c r="I95" t="s">
+        <v>188</v>
+      </c>
+      <c r="J95" t="s">
+        <v>31</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>559</v>
+      </c>
+      <c r="M95" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>561</v>
+      </c>
+      <c r="B96" t="s">
+        <v>562</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" t="s">
+        <v>563</v>
+      </c>
+      <c r="E96" t="s">
+        <v>536</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>31</v>
+      </c>
+      <c r="I96" t="s">
+        <v>188</v>
+      </c>
+      <c r="J96" t="s">
+        <v>31</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>564</v>
+      </c>
+      <c r="M96" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>566</v>
+      </c>
+      <c r="B97" t="s">
+        <v>567</v>
+      </c>
+      <c r="C97" t="s">
+        <v>154</v>
+      </c>
+      <c r="D97" t="s">
+        <v>568</v>
+      </c>
+      <c r="E97" t="s">
+        <v>536</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>31</v>
+      </c>
+      <c r="I97" t="s">
+        <v>188</v>
+      </c>
+      <c r="J97" t="s">
+        <v>31</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>569</v>
+      </c>
+      <c r="M97" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>571</v>
+      </c>
+      <c r="B98" t="s">
+        <v>572</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
+        <v>573</v>
+      </c>
+      <c r="E98" t="s">
+        <v>536</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>138</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>31</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>574</v>
+      </c>
+      <c r="M98" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>576</v>
+      </c>
+      <c r="B99" t="s">
+        <v>577</v>
+      </c>
+      <c r="C99" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" t="s">
+        <v>578</v>
+      </c>
+      <c r="E99" t="s">
+        <v>536</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>31</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>579</v>
+      </c>
+      <c r="M99" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>581</v>
+      </c>
+      <c r="B100" t="s">
+        <v>582</v>
+      </c>
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" t="s">
+        <v>583</v>
+      </c>
+      <c r="E100" t="s">
+        <v>536</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>131</v>
+      </c>
+      <c r="I100" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>584</v>
+      </c>
+      <c r="M100" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>586</v>
+      </c>
+      <c r="B101" t="s">
+        <v>587</v>
+      </c>
+      <c r="C101" t="s">
+        <v>87</v>
+      </c>
+      <c r="D101" t="s">
+        <v>588</v>
+      </c>
+      <c r="E101" t="s">
+        <v>536</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>422</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>589</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" t="s">
+        <v>590</v>
+      </c>
+      <c r="M101" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>592</v>
+      </c>
+      <c r="B102" t="s">
+        <v>593</v>
+      </c>
+      <c r="C102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" t="s">
+        <v>594</v>
+      </c>
+      <c r="E102" t="s">
+        <v>595</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>31</v>
+      </c>
+      <c r="I102" t="s">
+        <v>188</v>
+      </c>
+      <c r="J102" t="s">
+        <v>22</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>596</v>
+      </c>
+      <c r="M102" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>598</v>
+      </c>
+      <c r="B103" t="s">
+        <v>599</v>
+      </c>
+      <c r="C103" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" t="s">
+        <v>600</v>
+      </c>
+      <c r="E103" t="s">
+        <v>595</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>601</v>
+      </c>
+      <c r="I103" t="s">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s">
+        <v>22</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" t="s">
+        <v>602</v>
+      </c>
+      <c r="M103" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>604</v>
+      </c>
+      <c r="B104" t="s">
+        <v>605</v>
+      </c>
+      <c r="C104" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" t="s">
+        <v>606</v>
+      </c>
+      <c r="E104" t="s">
+        <v>595</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>37</v>
+      </c>
+      <c r="I104" t="s">
+        <v>21</v>
+      </c>
+      <c r="J104" t="s">
+        <v>22</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" t="s">
+        <v>607</v>
+      </c>
+      <c r="M104" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>609</v>
+      </c>
+      <c r="B105" t="s">
+        <v>610</v>
+      </c>
+      <c r="C105" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" t="s">
+        <v>611</v>
+      </c>
+      <c r="E105" t="s">
+        <v>595</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>77</v>
+      </c>
+      <c r="I105" t="s">
+        <v>21</v>
+      </c>
+      <c r="J105" t="s">
+        <v>22</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" t="s">
+        <v>612</v>
+      </c>
+      <c r="M105" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>614</v>
+      </c>
+      <c r="B106" t="s">
+        <v>615</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" t="s">
+        <v>616</v>
+      </c>
+      <c r="E106" t="s">
+        <v>595</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>156</v>
+      </c>
+      <c r="I106" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s">
+        <v>22</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" t="s">
+        <v>617</v>
+      </c>
+      <c r="M106" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>619</v>
+      </c>
+      <c r="B107" t="s">
+        <v>620</v>
+      </c>
+      <c r="C107" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" t="s">
+        <v>621</v>
+      </c>
+      <c r="E107" t="s">
+        <v>595</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s">
+        <v>31</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" t="s">
+        <v>622</v>
+      </c>
+      <c r="M107" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>624</v>
+      </c>
+      <c r="B108" t="s">
+        <v>625</v>
+      </c>
+      <c r="C108" t="s">
+        <v>154</v>
+      </c>
+      <c r="D108" t="s">
+        <v>626</v>
+      </c>
+      <c r="E108" t="s">
+        <v>595</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>77</v>
+      </c>
+      <c r="I108" t="s">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s">
+        <v>31</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" t="s">
+        <v>627</v>
+      </c>
+      <c r="M108" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>629</v>
+      </c>
+      <c r="B109" t="s">
+        <v>630</v>
+      </c>
+      <c r="C109" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" t="s">
+        <v>631</v>
+      </c>
+      <c r="E109" t="s">
+        <v>595</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>31</v>
+      </c>
+      <c r="I109" t="s">
+        <v>188</v>
+      </c>
+      <c r="J109" t="s">
+        <v>22</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" t="s">
+        <v>632</v>
+      </c>
+      <c r="M109" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>634</v>
+      </c>
+      <c r="B110" t="s">
+        <v>635</v>
+      </c>
+      <c r="C110" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" t="s">
+        <v>636</v>
+      </c>
+      <c r="E110" t="s">
+        <v>595</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>63</v>
+      </c>
+      <c r="I110" t="s">
+        <v>21</v>
+      </c>
+      <c r="J110" t="s">
+        <v>31</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" t="s">
+        <v>637</v>
+      </c>
+      <c r="M110" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>639</v>
+      </c>
+      <c r="B111" t="s">
+        <v>640</v>
+      </c>
+      <c r="C111" t="s">
+        <v>154</v>
+      </c>
+      <c r="D111" t="s">
+        <v>641</v>
+      </c>
+      <c r="E111" t="s">
+        <v>595</v>
+      </c>
+      <c r="F111" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" t="s">
+        <v>31</v>
+      </c>
+      <c r="I111" t="s">
+        <v>188</v>
+      </c>
+      <c r="J111" t="s">
+        <v>31</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" t="s">
+        <v>642</v>
+      </c>
+      <c r="M111" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>644</v>
+      </c>
+      <c r="B112" t="s">
+        <v>645</v>
+      </c>
+      <c r="C112" t="s">
+        <v>154</v>
+      </c>
+      <c r="D112" t="s">
+        <v>646</v>
+      </c>
+      <c r="E112" t="s">
+        <v>595</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>31</v>
+      </c>
+      <c r="I112" t="s">
+        <v>188</v>
+      </c>
+      <c r="J112" t="s">
+        <v>31</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" t="s">
+        <v>647</v>
+      </c>
+      <c r="M112" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>649</v>
+      </c>
+      <c r="B113" t="s">
+        <v>650</v>
+      </c>
+      <c r="C113" t="s">
+        <v>651</v>
+      </c>
+      <c r="D113" t="s">
+        <v>652</v>
+      </c>
+      <c r="E113" t="s">
+        <v>595</v>
+      </c>
+      <c r="F113" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" t="s">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s">
+        <v>22</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" t="s">
+        <v>653</v>
+      </c>
+      <c r="M113" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>655</v>
+      </c>
+      <c r="B114" t="s">
+        <v>656</v>
+      </c>
+      <c r="C114" t="s">
+        <v>657</v>
+      </c>
+      <c r="D114" t="s">
+        <v>658</v>
+      </c>
+      <c r="E114" t="s">
+        <v>595</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>131</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s">
+        <v>31</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" t="s">
+        <v>659</v>
+      </c>
+      <c r="M114" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>661</v>
+      </c>
+      <c r="B115" t="s">
+        <v>662</v>
+      </c>
+      <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" t="s">
+        <v>663</v>
+      </c>
+      <c r="E115" t="s">
+        <v>595</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s">
+        <v>31</v>
+      </c>
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" t="s">
+        <v>664</v>
+      </c>
+      <c r="M115" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>666</v>
+      </c>
+      <c r="B116" t="s">
+        <v>667</v>
+      </c>
+      <c r="C116" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" t="s">
+        <v>668</v>
+      </c>
+      <c r="E116" t="s">
+        <v>595</v>
+      </c>
+      <c r="F116" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
+        <v>77</v>
+      </c>
+      <c r="I116" t="s">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s">
+        <v>31</v>
+      </c>
+      <c r="K116" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" t="s">
+        <v>669</v>
+      </c>
+      <c r="M116" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>671</v>
+      </c>
+      <c r="B117" t="s">
+        <v>672</v>
+      </c>
+      <c r="C117" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" t="s">
+        <v>673</v>
+      </c>
+      <c r="E117" t="s">
+        <v>595</v>
+      </c>
+      <c r="F117" t="s">
+        <v>18</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" t="s">
+        <v>543</v>
+      </c>
+      <c r="I117" t="s">
+        <v>21</v>
+      </c>
+      <c r="J117" t="s">
+        <v>44</v>
+      </c>
+      <c r="K117" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" t="s">
+        <v>674</v>
+      </c>
+      <c r="M117" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>676</v>
+      </c>
+      <c r="B118" t="s">
+        <v>677</v>
+      </c>
+      <c r="C118" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" t="s">
+        <v>678</v>
+      </c>
+      <c r="E118" t="s">
+        <v>595</v>
+      </c>
+      <c r="F118" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>131</v>
+      </c>
+      <c r="I118" t="s">
+        <v>21</v>
+      </c>
+      <c r="J118" t="s">
+        <v>44</v>
+      </c>
+      <c r="K118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" t="s">
+        <v>679</v>
+      </c>
+      <c r="M118" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>681</v>
+      </c>
+      <c r="B119" t="s">
+        <v>682</v>
+      </c>
+      <c r="C119" t="s">
+        <v>683</v>
+      </c>
+      <c r="D119" t="s">
+        <v>684</v>
+      </c>
+      <c r="E119" t="s">
+        <v>595</v>
+      </c>
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
+      <c r="G119" t="s">
+        <v>19</v>
+      </c>
+      <c r="H119" t="s">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s">
+        <v>21</v>
+      </c>
+      <c r="J119" t="s">
+        <v>44</v>
+      </c>
+      <c r="K119" t="s">
+        <v>23</v>
+      </c>
+      <c r="L119" t="s">
+        <v>685</v>
+      </c>
+      <c r="M119" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>687</v>
+      </c>
+      <c r="B120" t="s">
+        <v>688</v>
+      </c>
+      <c r="C120" t="s">
+        <v>689</v>
+      </c>
+      <c r="D120" t="s">
+        <v>690</v>
+      </c>
+      <c r="E120" t="s">
+        <v>595</v>
+      </c>
+      <c r="F120" t="s">
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
+        <v>107</v>
+      </c>
+      <c r="I120" t="s">
+        <v>21</v>
+      </c>
+      <c r="J120" t="s">
+        <v>31</v>
+      </c>
+      <c r="K120" t="s">
+        <v>23</v>
+      </c>
+      <c r="L120" t="s">
+        <v>691</v>
+      </c>
+      <c r="M120" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>693</v>
+      </c>
+      <c r="B121" t="s">
+        <v>694</v>
+      </c>
+      <c r="C121" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" t="s">
+        <v>695</v>
+      </c>
+      <c r="E121" t="s">
+        <v>696</v>
+      </c>
+      <c r="F121" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" t="s">
+        <v>131</v>
+      </c>
+      <c r="I121" t="s">
+        <v>21</v>
+      </c>
+      <c r="J121" t="s">
+        <v>44</v>
+      </c>
+      <c r="K121" t="s">
+        <v>23</v>
+      </c>
+      <c r="L121" t="s">
+        <v>697</v>
+      </c>
+      <c r="M121" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>699</v>
+      </c>
+      <c r="B122" t="s">
+        <v>700</v>
+      </c>
+      <c r="C122" t="s">
+        <v>105</v>
+      </c>
+      <c r="D122" t="s">
+        <v>701</v>
+      </c>
+      <c r="E122" t="s">
+        <v>696</v>
+      </c>
+      <c r="F122" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
+        <v>31</v>
+      </c>
+      <c r="I122" t="s">
+        <v>188</v>
+      </c>
+      <c r="J122" t="s">
+        <v>22</v>
+      </c>
+      <c r="K122" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122" t="s">
+        <v>702</v>
+      </c>
+      <c r="M122" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>704</v>
+      </c>
+      <c r="B123" t="s">
+        <v>705</v>
+      </c>
+      <c r="C123" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" t="s">
+        <v>706</v>
+      </c>
+      <c r="E123" t="s">
+        <v>707</v>
+      </c>
+      <c r="F123" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>70</v>
+      </c>
+      <c r="I123" t="s">
+        <v>21</v>
+      </c>
+      <c r="J123" t="s">
+        <v>44</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>708</v>
+      </c>
+      <c r="M123" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>710</v>
+      </c>
+      <c r="B124" t="s">
+        <v>711</v>
+      </c>
+      <c r="C124" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" t="s">
+        <v>712</v>
+      </c>
+      <c r="E124" t="s">
+        <v>696</v>
+      </c>
+      <c r="F124" t="s">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>31</v>
+      </c>
+      <c r="I124" t="s">
+        <v>188</v>
+      </c>
+      <c r="J124" t="s">
+        <v>31</v>
+      </c>
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124" t="s">
+        <v>713</v>
+      </c>
+      <c r="M124" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>715</v>
+      </c>
+      <c r="B125" t="s">
+        <v>716</v>
+      </c>
+      <c r="C125" t="s">
+        <v>105</v>
+      </c>
+      <c r="D125" t="s">
+        <v>717</v>
+      </c>
+      <c r="E125" t="s">
+        <v>696</v>
+      </c>
+      <c r="F125" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" t="s">
+        <v>77</v>
+      </c>
+      <c r="I125" t="s">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s">
+        <v>44</v>
+      </c>
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125" t="s">
+        <v>718</v>
+      </c>
+      <c r="M125" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>720</v>
+      </c>
+      <c r="B126" t="s">
+        <v>721</v>
+      </c>
+      <c r="C126" t="s">
+        <v>178</v>
+      </c>
+      <c r="D126" t="s">
+        <v>722</v>
+      </c>
+      <c r="E126" t="s">
+        <v>696</v>
+      </c>
+      <c r="F126" t="s">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
+      </c>
+      <c r="H126" t="s">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s">
+        <v>366</v>
+      </c>
+      <c r="J126" t="s">
+        <v>31</v>
+      </c>
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126" t="s">
+        <v>723</v>
+      </c>
+      <c r="M126" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>725</v>
+      </c>
+      <c r="B127" t="s">
+        <v>726</v>
+      </c>
+      <c r="C127" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" t="s">
+        <v>727</v>
+      </c>
+      <c r="E127" t="s">
+        <v>728</v>
+      </c>
+      <c r="F127" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
+      </c>
+      <c r="H127" t="s">
+        <v>119</v>
+      </c>
+      <c r="I127" t="s">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s">
+        <v>729</v>
+      </c>
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127" t="s">
+        <v>730</v>
+      </c>
+      <c r="M127" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>732</v>
+      </c>
+      <c r="B128" t="s">
+        <v>733</v>
+      </c>
+      <c r="C128" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" t="s">
+        <v>734</v>
+      </c>
+      <c r="E128" t="s">
+        <v>735</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" t="s">
+        <v>162</v>
+      </c>
+      <c r="I128" t="s">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s">
+        <v>44</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128" t="s">
+        <v>736</v>
+      </c>
+      <c r="M128" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>738</v>
+      </c>
+      <c r="B129" t="s">
+        <v>739</v>
+      </c>
+      <c r="C129" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" t="s">
+        <v>740</v>
+      </c>
+      <c r="E129" t="s">
+        <v>728</v>
+      </c>
+      <c r="F129" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" t="s">
+        <v>50</v>
+      </c>
+      <c r="I129" t="s">
+        <v>21</v>
+      </c>
+      <c r="J129" t="s">
+        <v>71</v>
+      </c>
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129" t="s">
+        <v>741</v>
+      </c>
+      <c r="M129" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>743</v>
+      </c>
+      <c r="B130" t="s">
+        <v>744</v>
+      </c>
+      <c r="C130" t="s">
+        <v>105</v>
+      </c>
+      <c r="D130" t="s">
+        <v>745</v>
+      </c>
+      <c r="E130" t="s">
+        <v>728</v>
+      </c>
+      <c r="F130" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" t="s">
+        <v>162</v>
+      </c>
+      <c r="I130" t="s">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s">
+        <v>31</v>
+      </c>
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130" t="s">
+        <v>746</v>
+      </c>
+      <c r="M130" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>748</v>
+      </c>
+      <c r="B131" t="s">
+        <v>749</v>
+      </c>
+      <c r="C131" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" t="s">
+        <v>750</v>
+      </c>
+      <c r="E131" t="s">
+        <v>728</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" t="s">
+        <v>162</v>
+      </c>
+      <c r="I131" t="s">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s">
+        <v>44</v>
+      </c>
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131" t="s">
+        <v>751</v>
+      </c>
+      <c r="M131" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>753</v>
+      </c>
+      <c r="B132" t="s">
+        <v>754</v>
+      </c>
+      <c r="C132" t="s">
+        <v>178</v>
+      </c>
+      <c r="D132" t="s">
+        <v>755</v>
+      </c>
+      <c r="E132" t="s">
+        <v>728</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" t="s">
+        <v>77</v>
+      </c>
+      <c r="I132" t="s">
+        <v>756</v>
+      </c>
+      <c r="J132" t="s">
+        <v>31</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>757</v>
+      </c>
+      <c r="M132" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>759</v>
+      </c>
+      <c r="B133" t="s">
+        <v>760</v>
+      </c>
+      <c r="C133" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" t="s">
+        <v>761</v>
+      </c>
+      <c r="E133" t="s">
+        <v>735</v>
+      </c>
+      <c r="F133" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+      <c r="H133" t="s">
+        <v>119</v>
+      </c>
+      <c r="I133" t="s">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s">
+        <v>44</v>
+      </c>
+      <c r="K133" t="s">
+        <v>23</v>
+      </c>
+      <c r="L133" t="s">
+        <v>762</v>
+      </c>
+      <c r="M133" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>764</v>
+      </c>
+      <c r="B134" t="s">
+        <v>765</v>
+      </c>
+      <c r="C134" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" t="s">
+        <v>766</v>
+      </c>
+      <c r="E134" t="s">
+        <v>735</v>
+      </c>
+      <c r="F134" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>77</v>
+      </c>
+      <c r="I134" t="s">
+        <v>21</v>
+      </c>
+      <c r="J134" t="s">
+        <v>31</v>
+      </c>
+      <c r="K134" t="s">
+        <v>23</v>
+      </c>
+      <c r="L134" t="s">
+        <v>767</v>
+      </c>
+      <c r="M134" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>769</v>
+      </c>
+      <c r="B135" t="s">
+        <v>770</v>
+      </c>
+      <c r="C135" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135" t="s">
+        <v>771</v>
+      </c>
+      <c r="E135" t="s">
+        <v>735</v>
+      </c>
+      <c r="F135" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" t="s">
+        <v>162</v>
+      </c>
+      <c r="I135" t="s">
+        <v>21</v>
+      </c>
+      <c r="J135" t="s">
+        <v>132</v>
+      </c>
+      <c r="K135" t="s">
+        <v>23</v>
+      </c>
+      <c r="L135" t="s">
+        <v>772</v>
+      </c>
+      <c r="M135" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>774</v>
+      </c>
+      <c r="B136" t="s">
+        <v>775</v>
+      </c>
+      <c r="C136" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" t="s">
+        <v>776</v>
+      </c>
+      <c r="E136" t="s">
+        <v>735</v>
+      </c>
+      <c r="F136" t="s">
+        <v>18</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" t="s">
+        <v>138</v>
+      </c>
+      <c r="I136" t="s">
+        <v>21</v>
+      </c>
+      <c r="J136" t="s">
+        <v>44</v>
+      </c>
+      <c r="K136" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" t="s">
+        <v>777</v>
+      </c>
+      <c r="M136" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>779</v>
+      </c>
+      <c r="B137" t="s">
+        <v>780</v>
+      </c>
+      <c r="C137" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" t="s">
+        <v>781</v>
+      </c>
+      <c r="E137" t="s">
+        <v>735</v>
+      </c>
+      <c r="F137" t="s">
+        <v>18</v>
+      </c>
+      <c r="G137" t="s">
+        <v>19</v>
+      </c>
+      <c r="H137" t="s">
+        <v>20</v>
+      </c>
+      <c r="I137" t="s">
+        <v>21</v>
+      </c>
+      <c r="J137" t="s">
+        <v>44</v>
+      </c>
+      <c r="K137" t="s">
+        <v>23</v>
+      </c>
+      <c r="L137" t="s">
+        <v>782</v>
+      </c>
+      <c r="M137" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>784</v>
+      </c>
+      <c r="B138" t="s">
+        <v>785</v>
+      </c>
+      <c r="C138" t="s">
+        <v>105</v>
+      </c>
+      <c r="D138" t="s">
+        <v>786</v>
+      </c>
+      <c r="E138" t="s">
+        <v>735</v>
+      </c>
+      <c r="F138" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" t="s">
+        <v>63</v>
+      </c>
+      <c r="I138" t="s">
+        <v>21</v>
+      </c>
+      <c r="J138" t="s">
+        <v>245</v>
+      </c>
+      <c r="K138" t="s">
+        <v>23</v>
+      </c>
+      <c r="L138" t="s">
+        <v>787</v>
+      </c>
+      <c r="M138" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>789</v>
+      </c>
+      <c r="B139" t="s">
+        <v>790</v>
+      </c>
+      <c r="C139" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" t="s">
+        <v>791</v>
+      </c>
+      <c r="E139" t="s">
+        <v>735</v>
+      </c>
+      <c r="F139" t="s">
+        <v>18</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
+      </c>
+      <c r="H139" t="s">
+        <v>77</v>
+      </c>
+      <c r="I139" t="s">
+        <v>21</v>
+      </c>
+      <c r="J139" t="s">
+        <v>31</v>
+      </c>
+      <c r="K139" t="s">
+        <v>23</v>
+      </c>
+      <c r="L139" t="s">
+        <v>792</v>
+      </c>
+      <c r="M139" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>794</v>
+      </c>
+      <c r="B140" t="s">
+        <v>795</v>
+      </c>
+      <c r="C140" t="s">
+        <v>15</v>
+      </c>
+      <c r="D140" t="s">
+        <v>796</v>
+      </c>
+      <c r="E140" t="s">
+        <v>735</v>
+      </c>
+      <c r="F140" t="s">
+        <v>18</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140" t="s">
+        <v>77</v>
+      </c>
+      <c r="I140" t="s">
+        <v>21</v>
+      </c>
+      <c r="J140" t="s">
+        <v>44</v>
+      </c>
+      <c r="K140" t="s">
+        <v>23</v>
+      </c>
+      <c r="L140" t="s">
+        <v>797</v>
+      </c>
+      <c r="M140" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>799</v>
+      </c>
+      <c r="B141" t="s">
+        <v>800</v>
+      </c>
+      <c r="C141" t="s">
+        <v>440</v>
+      </c>
+      <c r="D141" t="s">
+        <v>801</v>
+      </c>
+      <c r="E141" t="s">
+        <v>735</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" t="s">
+        <v>19</v>
+      </c>
+      <c r="H141" t="s">
+        <v>77</v>
+      </c>
+      <c r="I141" t="s">
+        <v>21</v>
+      </c>
+      <c r="J141" t="s">
+        <v>31</v>
+      </c>
+      <c r="K141" t="s">
+        <v>23</v>
+      </c>
+      <c r="L141" t="s">
+        <v>802</v>
+      </c>
+      <c r="M141" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>804</v>
+      </c>
+      <c r="B142" t="s">
+        <v>805</v>
+      </c>
+      <c r="C142" t="s">
+        <v>440</v>
+      </c>
+      <c r="D142" t="s">
+        <v>806</v>
+      </c>
+      <c r="E142" t="s">
+        <v>735</v>
+      </c>
+      <c r="F142" t="s">
+        <v>18</v>
+      </c>
+      <c r="G142" t="s">
+        <v>19</v>
+      </c>
+      <c r="H142" t="s">
+        <v>807</v>
+      </c>
+      <c r="I142" t="s">
+        <v>21</v>
+      </c>
+      <c r="J142" t="s">
+        <v>71</v>
+      </c>
+      <c r="K142" t="s">
+        <v>23</v>
+      </c>
+      <c r="L142" t="s">
+        <v>808</v>
+      </c>
+      <c r="M142" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>810</v>
+      </c>
+      <c r="B143" t="s">
+        <v>811</v>
+      </c>
+      <c r="C143" t="s">
+        <v>178</v>
+      </c>
+      <c r="D143" t="s">
+        <v>812</v>
+      </c>
+      <c r="E143" t="s">
+        <v>735</v>
+      </c>
+      <c r="F143" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" t="s">
+        <v>19</v>
+      </c>
+      <c r="H143" t="s">
+        <v>138</v>
+      </c>
+      <c r="I143" t="s">
+        <v>813</v>
+      </c>
+      <c r="J143" t="s">
+        <v>814</v>
+      </c>
+      <c r="K143" t="s">
+        <v>23</v>
+      </c>
+      <c r="L143" t="s">
+        <v>815</v>
+      </c>
+      <c r="M143" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>817</v>
+      </c>
+      <c r="B144" t="s">
+        <v>818</v>
+      </c>
+      <c r="C144" t="s">
+        <v>28</v>
+      </c>
+      <c r="D144" t="s">
+        <v>819</v>
+      </c>
+      <c r="E144" t="s">
+        <v>735</v>
+      </c>
+      <c r="F144" t="s">
+        <v>18</v>
+      </c>
+      <c r="G144" t="s">
+        <v>19</v>
+      </c>
+      <c r="H144" t="s">
+        <v>77</v>
+      </c>
+      <c r="I144" t="s">
+        <v>21</v>
+      </c>
+      <c r="J144" t="s">
+        <v>31</v>
+      </c>
+      <c r="K144" t="s">
+        <v>23</v>
+      </c>
+      <c r="L144" t="s">
+        <v>820</v>
+      </c>
+      <c r="M144" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>822</v>
+      </c>
+      <c r="B145" t="s">
+        <v>823</v>
+      </c>
+      <c r="C145" t="s">
+        <v>87</v>
+      </c>
+      <c r="D145" t="s">
+        <v>824</v>
+      </c>
+      <c r="E145" t="s">
+        <v>735</v>
+      </c>
+      <c r="F145" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" t="s">
+        <v>19</v>
+      </c>
+      <c r="H145" t="s">
+        <v>77</v>
+      </c>
+      <c r="I145" t="s">
+        <v>21</v>
+      </c>
+      <c r="J145" t="s">
+        <v>173</v>
+      </c>
+      <c r="K145" t="s">
+        <v>23</v>
+      </c>
+      <c r="L145" t="s">
+        <v>825</v>
+      </c>
+      <c r="M145" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>827</v>
+      </c>
+      <c r="B146" t="s">
+        <v>828</v>
+      </c>
+      <c r="C146" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" t="s">
+        <v>829</v>
+      </c>
+      <c r="E146" t="s">
+        <v>735</v>
+      </c>
+      <c r="F146" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" t="s">
+        <v>31</v>
+      </c>
+      <c r="I146" t="s">
+        <v>188</v>
+      </c>
+      <c r="J146" t="s">
+        <v>31</v>
+      </c>
+      <c r="K146" t="s">
+        <v>23</v>
+      </c>
+      <c r="L146" t="s">
+        <v>830</v>
+      </c>
+      <c r="M146" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>832</v>
+      </c>
+      <c r="B147" t="s">
+        <v>833</v>
+      </c>
+      <c r="C147" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" t="s">
+        <v>834</v>
+      </c>
+      <c r="E147" t="s">
+        <v>735</v>
+      </c>
+      <c r="F147" t="s">
+        <v>18</v>
+      </c>
+      <c r="G147" t="s">
+        <v>19</v>
+      </c>
+      <c r="H147" t="s">
+        <v>77</v>
+      </c>
+      <c r="I147" t="s">
+        <v>21</v>
+      </c>
+      <c r="J147" t="s">
+        <v>44</v>
+      </c>
+      <c r="K147" t="s">
+        <v>23</v>
+      </c>
+      <c r="L147" t="s">
+        <v>835</v>
+      </c>
+      <c r="M147" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>837</v>
+      </c>
+      <c r="B148" t="s">
+        <v>838</v>
+      </c>
+      <c r="C148" t="s">
+        <v>105</v>
+      </c>
+      <c r="D148" t="s">
+        <v>839</v>
+      </c>
+      <c r="E148" t="s">
+        <v>840</v>
+      </c>
+      <c r="F148" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148" t="s">
+        <v>37</v>
+      </c>
+      <c r="I148" t="s">
+        <v>21</v>
+      </c>
+      <c r="J148" t="s">
+        <v>31</v>
+      </c>
+      <c r="K148" t="s">
+        <v>23</v>
+      </c>
+      <c r="L148" t="s">
+        <v>841</v>
+      </c>
+      <c r="M148" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>843</v>
+      </c>
+      <c r="B149" t="s">
+        <v>844</v>
+      </c>
+      <c r="C149" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" t="s">
+        <v>845</v>
+      </c>
+      <c r="E149" t="s">
+        <v>840</v>
+      </c>
+      <c r="F149" t="s">
+        <v>18</v>
+      </c>
+      <c r="G149" t="s">
+        <v>19</v>
+      </c>
+      <c r="H149" t="s">
+        <v>77</v>
+      </c>
+      <c r="I149" t="s">
+        <v>21</v>
+      </c>
+      <c r="J149" t="s">
+        <v>44</v>
+      </c>
+      <c r="K149" t="s">
+        <v>23</v>
+      </c>
+      <c r="L149" t="s">
+        <v>846</v>
+      </c>
+      <c r="M149" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>848</v>
+      </c>
+      <c r="B150" t="s">
+        <v>849</v>
+      </c>
+      <c r="C150" t="s">
+        <v>15</v>
+      </c>
+      <c r="D150" t="s">
+        <v>850</v>
+      </c>
+      <c r="E150" t="s">
+        <v>851</v>
+      </c>
+      <c r="F150" t="s">
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150" t="s">
+        <v>162</v>
+      </c>
+      <c r="I150" t="s">
+        <v>21</v>
+      </c>
+      <c r="J150" t="s">
+        <v>44</v>
+      </c>
+      <c r="K150" t="s">
+        <v>23</v>
+      </c>
+      <c r="L150" t="s">
+        <v>852</v>
+      </c>
+      <c r="M150" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>854</v>
+      </c>
+      <c r="B151" t="s">
+        <v>855</v>
+      </c>
+      <c r="C151" t="s">
+        <v>15</v>
+      </c>
+      <c r="D151" t="s">
+        <v>856</v>
+      </c>
+      <c r="E151" t="s">
+        <v>840</v>
+      </c>
+      <c r="F151" t="s">
+        <v>18</v>
+      </c>
+      <c r="G151" t="s">
+        <v>19</v>
+      </c>
+      <c r="H151" t="s">
+        <v>77</v>
+      </c>
+      <c r="I151" t="s">
+        <v>21</v>
+      </c>
+      <c r="J151" t="s">
+        <v>44</v>
+      </c>
+      <c r="K151" t="s">
+        <v>23</v>
+      </c>
+      <c r="L151" t="s">
+        <v>857</v>
+      </c>
+      <c r="M151" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>859</v>
+      </c>
+      <c r="B152" t="s">
+        <v>860</v>
+      </c>
+      <c r="C152" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152" t="s">
+        <v>861</v>
+      </c>
+      <c r="E152" t="s">
+        <v>840</v>
+      </c>
+      <c r="F152" t="s">
+        <v>18</v>
+      </c>
+      <c r="G152" t="s">
+        <v>19</v>
+      </c>
+      <c r="H152" t="s">
+        <v>77</v>
+      </c>
+      <c r="I152" t="s">
+        <v>21</v>
+      </c>
+      <c r="J152" t="s">
+        <v>44</v>
+      </c>
+      <c r="K152" t="s">
+        <v>23</v>
+      </c>
+      <c r="L152" t="s">
+        <v>862</v>
+      </c>
+      <c r="M152" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>864</v>
+      </c>
+      <c r="B153" t="s">
+        <v>865</v>
+      </c>
+      <c r="C153" t="s">
+        <v>15</v>
+      </c>
+      <c r="D153" t="s">
+        <v>866</v>
+      </c>
+      <c r="E153" t="s">
+        <v>840</v>
+      </c>
+      <c r="F153" t="s">
+        <v>18</v>
+      </c>
+      <c r="G153" t="s">
+        <v>19</v>
+      </c>
+      <c r="H153" t="s">
+        <v>31</v>
+      </c>
+      <c r="I153" t="s">
+        <v>188</v>
+      </c>
+      <c r="J153" t="s">
+        <v>31</v>
+      </c>
+      <c r="K153" t="s">
+        <v>23</v>
+      </c>
+      <c r="L153" t="s">
+        <v>867</v>
+      </c>
+      <c r="M153" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>869</v>
+      </c>
+      <c r="B154" t="s">
+        <v>870</v>
+      </c>
+      <c r="C154" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" t="s">
+        <v>871</v>
+      </c>
+      <c r="E154" t="s">
+        <v>840</v>
+      </c>
+      <c r="F154" t="s">
+        <v>18</v>
+      </c>
+      <c r="G154" t="s">
+        <v>19</v>
+      </c>
+      <c r="H154" t="s">
+        <v>872</v>
+      </c>
+      <c r="I154" t="s">
+        <v>21</v>
+      </c>
+      <c r="J154" t="s">
+        <v>31</v>
+      </c>
+      <c r="K154" t="s">
+        <v>23</v>
+      </c>
+      <c r="L154" t="s">
+        <v>873</v>
+      </c>
+      <c r="M154" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>875</v>
+      </c>
+      <c r="B155" t="s">
+        <v>876</v>
+      </c>
+      <c r="C155" t="s">
+        <v>343</v>
+      </c>
+      <c r="D155" t="s">
+        <v>877</v>
+      </c>
+      <c r="E155" t="s">
+        <v>878</v>
+      </c>
+      <c r="F155" t="s">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>19</v>
+      </c>
+      <c r="H155" t="s">
+        <v>879</v>
+      </c>
+      <c r="I155" t="s">
+        <v>21</v>
+      </c>
+      <c r="J155" t="s">
+        <v>44</v>
+      </c>
+      <c r="K155" t="s">
+        <v>23</v>
+      </c>
+      <c r="L155" t="s">
+        <v>880</v>
+      </c>
+      <c r="M155" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>882</v>
+      </c>
+      <c r="B156" t="s">
+        <v>883</v>
+      </c>
+      <c r="C156" t="s">
+        <v>15</v>
+      </c>
+      <c r="D156" t="s">
+        <v>884</v>
+      </c>
+      <c r="E156" t="s">
+        <v>840</v>
+      </c>
+      <c r="F156" t="s">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" t="s">
+        <v>77</v>
+      </c>
+      <c r="I156" t="s">
+        <v>21</v>
+      </c>
+      <c r="J156" t="s">
+        <v>31</v>
+      </c>
+      <c r="K156" t="s">
+        <v>23</v>
+      </c>
+      <c r="L156" t="s">
+        <v>885</v>
+      </c>
+      <c r="M156" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>887</v>
+      </c>
+      <c r="B157" t="s">
+        <v>888</v>
+      </c>
+      <c r="C157" t="s">
+        <v>154</v>
+      </c>
+      <c r="D157" t="s">
+        <v>889</v>
+      </c>
+      <c r="E157" t="s">
+        <v>840</v>
+      </c>
+      <c r="F157" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>19</v>
+      </c>
+      <c r="H157" t="s">
+        <v>31</v>
+      </c>
+      <c r="I157" t="s">
+        <v>188</v>
+      </c>
+      <c r="J157" t="s">
+        <v>31</v>
+      </c>
+      <c r="K157" t="s">
+        <v>23</v>
+      </c>
+      <c r="L157" t="s">
+        <v>890</v>
+      </c>
+      <c r="M157" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>892</v>
+      </c>
+      <c r="B158" t="s">
+        <v>893</v>
+      </c>
+      <c r="C158" t="s">
+        <v>154</v>
+      </c>
+      <c r="D158" t="s">
+        <v>894</v>
+      </c>
+      <c r="E158" t="s">
+        <v>840</v>
+      </c>
+      <c r="F158" t="s">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" t="s">
+        <v>31</v>
+      </c>
+      <c r="I158" t="s">
+        <v>188</v>
+      </c>
+      <c r="J158" t="s">
+        <v>44</v>
+      </c>
+      <c r="K158" t="s">
+        <v>23</v>
+      </c>
+      <c r="L158" t="s">
+        <v>895</v>
+      </c>
+      <c r="M158" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>897</v>
+      </c>
+      <c r="B159" t="s">
+        <v>898</v>
+      </c>
+      <c r="C159" t="s">
+        <v>15</v>
+      </c>
+      <c r="D159" t="s">
+        <v>899</v>
+      </c>
+      <c r="E159" t="s">
+        <v>840</v>
+      </c>
+      <c r="F159" t="s">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>19</v>
+      </c>
+      <c r="H159" t="s">
+        <v>872</v>
+      </c>
+      <c r="I159" t="s">
+        <v>21</v>
+      </c>
+      <c r="J159" t="s">
+        <v>31</v>
+      </c>
+      <c r="K159" t="s">
+        <v>23</v>
+      </c>
+      <c r="L159" t="s">
+        <v>900</v>
+      </c>
+      <c r="M159" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>902</v>
+      </c>
+      <c r="B160" t="s">
+        <v>903</v>
+      </c>
+      <c r="C160" t="s">
+        <v>440</v>
+      </c>
+      <c r="D160" t="s">
+        <v>904</v>
+      </c>
+      <c r="E160" t="s">
+        <v>840</v>
+      </c>
+      <c r="F160" t="s">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" t="s">
+        <v>77</v>
+      </c>
+      <c r="I160" t="s">
+        <v>21</v>
+      </c>
+      <c r="J160" t="s">
+        <v>44</v>
+      </c>
+      <c r="K160" t="s">
+        <v>23</v>
+      </c>
+      <c r="L160" t="s">
+        <v>905</v>
+      </c>
+      <c r="M160" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>907</v>
+      </c>
+      <c r="B161" t="s">
+        <v>908</v>
+      </c>
+      <c r="C161" t="s">
+        <v>440</v>
+      </c>
+      <c r="D161" t="s">
+        <v>909</v>
+      </c>
+      <c r="E161" t="s">
+        <v>840</v>
+      </c>
+      <c r="F161" t="s">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>19</v>
+      </c>
+      <c r="H161" t="s">
+        <v>77</v>
+      </c>
+      <c r="I161" t="s">
+        <v>21</v>
+      </c>
+      <c r="J161" t="s">
+        <v>44</v>
+      </c>
+      <c r="K161" t="s">
+        <v>23</v>
+      </c>
+      <c r="L161" t="s">
+        <v>910</v>
+      </c>
+      <c r="M161" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>912</v>
+      </c>
+      <c r="B162" t="s">
+        <v>913</v>
+      </c>
+      <c r="C162" t="s">
+        <v>440</v>
+      </c>
+      <c r="D162" t="s">
+        <v>914</v>
+      </c>
+      <c r="E162" t="s">
+        <v>840</v>
+      </c>
+      <c r="F162" t="s">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" t="s">
+        <v>31</v>
+      </c>
+      <c r="I162" t="s">
+        <v>188</v>
+      </c>
+      <c r="J162" t="s">
+        <v>31</v>
+      </c>
+      <c r="K162" t="s">
+        <v>23</v>
+      </c>
+      <c r="L162" t="s">
+        <v>915</v>
+      </c>
+      <c r="M162" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>917</v>
+      </c>
+      <c r="B163" t="s">
+        <v>918</v>
+      </c>
+      <c r="C163" t="s">
+        <v>440</v>
+      </c>
+      <c r="D163" t="s">
+        <v>919</v>
+      </c>
+      <c r="E163" t="s">
+        <v>840</v>
+      </c>
+      <c r="F163" t="s">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163" t="s">
+        <v>37</v>
+      </c>
+      <c r="I163" t="s">
+        <v>21</v>
+      </c>
+      <c r="J163" t="s">
+        <v>44</v>
+      </c>
+      <c r="K163" t="s">
+        <v>23</v>
+      </c>
+      <c r="L163" t="s">
+        <v>920</v>
+      </c>
+      <c r="M163" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>922</v>
+      </c>
+      <c r="B164" t="s">
+        <v>923</v>
+      </c>
+      <c r="C164" t="s">
+        <v>15</v>
+      </c>
+      <c r="D164" t="s">
+        <v>924</v>
+      </c>
+      <c r="E164" t="s">
+        <v>840</v>
+      </c>
+      <c r="F164" t="s">
+        <v>18</v>
+      </c>
+      <c r="G164" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" t="s">
+        <v>31</v>
+      </c>
+      <c r="I164" t="s">
+        <v>188</v>
+      </c>
+      <c r="J164" t="s">
+        <v>31</v>
+      </c>
+      <c r="K164" t="s">
+        <v>23</v>
+      </c>
+      <c r="L164" t="s">
+        <v>925</v>
+      </c>
+      <c r="M164" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>927</v>
+      </c>
+      <c r="B165" t="s">
+        <v>928</v>
+      </c>
+      <c r="C165" t="s">
+        <v>15</v>
+      </c>
+      <c r="D165" t="s">
+        <v>929</v>
+      </c>
+      <c r="E165" t="s">
+        <v>840</v>
+      </c>
+      <c r="F165" t="s">
+        <v>18</v>
+      </c>
+      <c r="G165" t="s">
+        <v>19</v>
+      </c>
+      <c r="H165" t="s">
+        <v>301</v>
+      </c>
+      <c r="I165" t="s">
+        <v>21</v>
+      </c>
+      <c r="J165" t="s">
+        <v>44</v>
+      </c>
+      <c r="K165" t="s">
+        <v>23</v>
+      </c>
+      <c r="L165" t="s">
+        <v>930</v>
+      </c>
+      <c r="M165" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>932</v>
+      </c>
+      <c r="B166" t="s">
+        <v>933</v>
+      </c>
+      <c r="C166" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" t="s">
+        <v>934</v>
+      </c>
+      <c r="E166" t="s">
+        <v>840</v>
+      </c>
+      <c r="F166" t="s">
+        <v>18</v>
+      </c>
+      <c r="G166" t="s">
+        <v>19</v>
+      </c>
+      <c r="H166" t="s">
+        <v>77</v>
+      </c>
+      <c r="I166" t="s">
+        <v>21</v>
+      </c>
+      <c r="J166" t="s">
+        <v>935</v>
+      </c>
+      <c r="K166" t="s">
+        <v>23</v>
+      </c>
+      <c r="L166" t="s">
+        <v>936</v>
+      </c>
+      <c r="M166" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>938</v>
+      </c>
+      <c r="B167" t="s">
+        <v>939</v>
+      </c>
+      <c r="C167" t="s">
+        <v>28</v>
+      </c>
+      <c r="D167" t="s">
+        <v>940</v>
+      </c>
+      <c r="E167" t="s">
+        <v>840</v>
+      </c>
+      <c r="F167" t="s">
+        <v>18</v>
+      </c>
+      <c r="G167" t="s">
+        <v>19</v>
+      </c>
+      <c r="H167" t="s">
+        <v>77</v>
+      </c>
+      <c r="I167" t="s">
+        <v>21</v>
+      </c>
+      <c r="J167" t="s">
+        <v>31</v>
+      </c>
+      <c r="K167" t="s">
+        <v>23</v>
+      </c>
+      <c r="L167" t="s">
+        <v>941</v>
+      </c>
+      <c r="M167" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>943</v>
+      </c>
+      <c r="B168" t="s">
+        <v>944</v>
+      </c>
+      <c r="C168" t="s">
+        <v>15</v>
+      </c>
+      <c r="D168" t="s">
+        <v>945</v>
+      </c>
+      <c r="E168" t="s">
+        <v>840</v>
+      </c>
+      <c r="F168" t="s">
+        <v>18</v>
+      </c>
+      <c r="G168" t="s">
+        <v>19</v>
+      </c>
+      <c r="H168" t="s">
+        <v>107</v>
+      </c>
+      <c r="I168" t="s">
+        <v>21</v>
+      </c>
+      <c r="J168" t="s">
+        <v>22</v>
+      </c>
+      <c r="K168" t="s">
+        <v>23</v>
+      </c>
+      <c r="L168" t="s">
+        <v>946</v>
+      </c>
+      <c r="M168" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>948</v>
+      </c>
+      <c r="B169" t="s">
+        <v>949</v>
+      </c>
+      <c r="C169" t="s">
+        <v>15</v>
+      </c>
+      <c r="D169" t="s">
+        <v>950</v>
+      </c>
+      <c r="E169" t="s">
+        <v>840</v>
+      </c>
+      <c r="F169" t="s">
+        <v>18</v>
+      </c>
+      <c r="G169" t="s">
+        <v>19</v>
+      </c>
+      <c r="H169" t="s">
+        <v>77</v>
+      </c>
+      <c r="I169" t="s">
+        <v>21</v>
+      </c>
+      <c r="J169" t="s">
+        <v>31</v>
+      </c>
+      <c r="K169" t="s">
+        <v>23</v>
+      </c>
+      <c r="L169" t="s">
+        <v>951</v>
+      </c>
+      <c r="M169" t="s">
+        <v>952</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/FL.xlsx
+++ b/Sajjad data/by_country_and_state/USA/FL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2197" uniqueCount="953">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="979">
   <si>
     <t>Business Name</t>
   </si>
@@ -2870,6 +2870,84 @@
   </si>
   <si>
     <t>2026-10-24T23:06:39.330Z</t>
+  </si>
+  <si>
+    <t>Dr. Ivette M. Ramos, DMD</t>
+  </si>
+  <si>
+    <t>(352) 376-6366</t>
+  </si>
+  <si>
+    <t>3731 NW 40th Terrace Ste A, Gainesville, FL 32606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ivette+M.+Ramos,+DMD/data=!4m7!3m6!1s0x88e8a4caf41bdc23:0xab72c890114c3d50!8m2!3d29.6876421!4d-82.3861247!16s%2Fg%2F1tq6f9pp!19sChIJI9wb9Mqk6IgRUD1MEZDIcqs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:30:53.510Z</t>
+  </si>
+  <si>
+    <t>Lan T. Tran, DMD</t>
+  </si>
+  <si>
+    <t>(352) 373-1884</t>
+  </si>
+  <si>
+    <t>1014 NW 23rd Ave, Gainesville, FL 32609</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lan+T.+Tran,+DMD/data=!4m7!3m6!1s0x88e8a46575ea7987:0xbbb8c876d5f25243!8m2!3d29.6741945!4d-82.33542!16s%2Fg%2F1tk70b6d!19sChIJh3nqdWWk6IgRQ1Ly1XbIuLs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:08.096Z</t>
+  </si>
+  <si>
+    <t>Florida Dental Center</t>
+  </si>
+  <si>
+    <t>(786) 598-6960</t>
+  </si>
+  <si>
+    <t>NW 21st Ln B, Gainesville, FL 32601</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Florida+Dental+Center/data=!4m7!3m6!1s0x88e8a38cc274f3f3:0x83e09b1d0be2437a!8m2!3d29.6516467!4d-82.3247426!16s%2Fg%2F11flbfxf2p!19sChIJ8_N0woyj6IgRekPiCx2b4IM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:10.655Z</t>
+  </si>
+  <si>
+    <t>Dr. Sujin Ju</t>
+  </si>
+  <si>
+    <t>(352) 226-8268</t>
+  </si>
+  <si>
+    <t>150 NW 75 Dr Ste B, Gainesville, FL 32607</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sujin+Ju/data=!4m7!3m6!1s0x88e8bc85772baaab:0x8e87c85f4f76ef39!8m2!3d29.6543424!4d-82.4234842!16s%2Fg%2F11k3pxff_d!19sChIJq6ord4W86IgROe92T1_Ih44?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:31:59.385Z</t>
+  </si>
+  <si>
+    <t>Dr. Caleb J. King III, DDS</t>
+  </si>
+  <si>
+    <t>(352) 376-5155</t>
+  </si>
+  <si>
+    <t>5014 NW 27th Ct, Gainesville, FL 32606</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; MondayClosed; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Caleb+J.+King+III,+DDS/data=!4m7!3m6!1s0x88e8bb4f030eeb13:0x12d3536e46067d60!8m2!3d29.6783488!4d-82.3970072!16s%2Fg%2F1tltn60l!19sChIJE-sOA0-76IgRYH0GRm5T0xI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:32:04.163Z</t>
   </si>
 </sst>
 </file>
@@ -3250,7 +3328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M169"/>
+  <dimension ref="A1:M174"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -10196,6 +10274,211 @@
         <v>952</v>
       </c>
     </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>953</v>
+      </c>
+      <c r="B170" t="s">
+        <v>954</v>
+      </c>
+      <c r="C170" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" t="s">
+        <v>955</v>
+      </c>
+      <c r="E170" t="s">
+        <v>840</v>
+      </c>
+      <c r="F170" t="s">
+        <v>18</v>
+      </c>
+      <c r="G170" t="s">
+        <v>19</v>
+      </c>
+      <c r="H170" t="s">
+        <v>872</v>
+      </c>
+      <c r="I170" t="s">
+        <v>21</v>
+      </c>
+      <c r="J170" t="s">
+        <v>31</v>
+      </c>
+      <c r="K170" t="s">
+        <v>23</v>
+      </c>
+      <c r="L170" t="s">
+        <v>956</v>
+      </c>
+      <c r="M170" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>958</v>
+      </c>
+      <c r="B171" t="s">
+        <v>959</v>
+      </c>
+      <c r="C171" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" t="s">
+        <v>960</v>
+      </c>
+      <c r="E171" t="s">
+        <v>840</v>
+      </c>
+      <c r="F171" t="s">
+        <v>18</v>
+      </c>
+      <c r="G171" t="s">
+        <v>19</v>
+      </c>
+      <c r="H171" t="s">
+        <v>879</v>
+      </c>
+      <c r="I171" t="s">
+        <v>21</v>
+      </c>
+      <c r="J171" t="s">
+        <v>44</v>
+      </c>
+      <c r="K171" t="s">
+        <v>23</v>
+      </c>
+      <c r="L171" t="s">
+        <v>961</v>
+      </c>
+      <c r="M171" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>963</v>
+      </c>
+      <c r="B172" t="s">
+        <v>964</v>
+      </c>
+      <c r="C172" t="s">
+        <v>105</v>
+      </c>
+      <c r="D172" t="s">
+        <v>965</v>
+      </c>
+      <c r="E172" t="s">
+        <v>840</v>
+      </c>
+      <c r="F172" t="s">
+        <v>18</v>
+      </c>
+      <c r="G172" t="s">
+        <v>19</v>
+      </c>
+      <c r="H172" t="s">
+        <v>31</v>
+      </c>
+      <c r="I172" t="s">
+        <v>188</v>
+      </c>
+      <c r="J172" t="s">
+        <v>31</v>
+      </c>
+      <c r="K172" t="s">
+        <v>23</v>
+      </c>
+      <c r="L172" t="s">
+        <v>966</v>
+      </c>
+      <c r="M172" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>968</v>
+      </c>
+      <c r="B173" t="s">
+        <v>969</v>
+      </c>
+      <c r="C173" t="s">
+        <v>15</v>
+      </c>
+      <c r="D173" t="s">
+        <v>970</v>
+      </c>
+      <c r="E173" t="s">
+        <v>840</v>
+      </c>
+      <c r="F173" t="s">
+        <v>18</v>
+      </c>
+      <c r="G173" t="s">
+        <v>19</v>
+      </c>
+      <c r="H173" t="s">
+        <v>77</v>
+      </c>
+      <c r="I173" t="s">
+        <v>21</v>
+      </c>
+      <c r="J173" t="s">
+        <v>31</v>
+      </c>
+      <c r="K173" t="s">
+        <v>23</v>
+      </c>
+      <c r="L173" t="s">
+        <v>971</v>
+      </c>
+      <c r="M173" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>973</v>
+      </c>
+      <c r="B174" t="s">
+        <v>974</v>
+      </c>
+      <c r="C174" t="s">
+        <v>178</v>
+      </c>
+      <c r="D174" t="s">
+        <v>975</v>
+      </c>
+      <c r="E174" t="s">
+        <v>840</v>
+      </c>
+      <c r="F174" t="s">
+        <v>18</v>
+      </c>
+      <c r="G174" t="s">
+        <v>19</v>
+      </c>
+      <c r="H174" t="s">
+        <v>31</v>
+      </c>
+      <c r="I174" t="s">
+        <v>366</v>
+      </c>
+      <c r="J174" t="s">
+        <v>976</v>
+      </c>
+      <c r="K174" t="s">
+        <v>23</v>
+      </c>
+      <c r="L174" t="s">
+        <v>977</v>
+      </c>
+      <c r="M174" t="s">
+        <v>978</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
